--- a/research/traditional_assets/database/data/russia/russia_steel.xlsx
+++ b/research/traditional_assets/database/data/russia/russia_steel.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1277362206402269</v>
+        <v>0.1275167481989464</v>
       </c>
       <c r="C2">
-        <v>24.4</v>
+        <v>24.16699474804589</v>
       </c>
       <c r="D2">
-        <v>24.331</v>
+        <v>24.34199474804589</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="G2">
         <v>0.06900000000000001</v>
@@ -1439,28 +1439,28 @@
         <v>32.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0122732</v>
       </c>
       <c r="N2">
-        <v>32.9</v>
+        <v>32.8877268</v>
       </c>
       <c r="O2">
-        <v>6.58</v>
+        <v>6.577545359999999</v>
       </c>
       <c r="P2">
-        <v>26.32</v>
+        <v>26.31018144</v>
       </c>
       <c r="Q2">
-        <v>30.72</v>
+        <v>30.71018144</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1277362206402269</v>
+        <v>0.1283983315140873</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9895067279752562</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>2680.637486556073</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1275167481989464</v>
+        <v>0.1272972757576659</v>
       </c>
       <c r="C3">
-        <v>24.16699474804589</v>
+        <v>23.9339994372479</v>
       </c>
       <c r="D3">
-        <v>24.34199474804589</v>
+        <v>24.3529994372479</v>
       </c>
       <c r="E3">
-        <v>0.244</v>
+        <v>0.488</v>
       </c>
       <c r="F3">
-        <v>0.244</v>
+        <v>0.488</v>
       </c>
       <c r="G3">
         <v>0.06900000000000001</v>
@@ -1521,28 +1521,28 @@
         <v>32.9</v>
       </c>
       <c r="M3">
-        <v>0.0122732</v>
+        <v>0.0245464</v>
       </c>
       <c r="N3">
-        <v>32.8877268</v>
+        <v>32.8754536</v>
       </c>
       <c r="O3">
-        <v>6.577545359999999</v>
+        <v>6.57509072</v>
       </c>
       <c r="P3">
-        <v>26.31018144</v>
+        <v>26.30036288</v>
       </c>
       <c r="Q3">
-        <v>30.71018144</v>
+        <v>30.70036288</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1283983315140873</v>
+        <v>0.1290739548547612</v>
       </c>
       <c r="T3">
-        <v>0.9895067279752562</v>
+        <v>0.9976005215049707</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>2680.637486556073</v>
+        <v>1340.318743278037</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1272972757576659</v>
+        <v>0.1270778033163855</v>
       </c>
       <c r="C4">
-        <v>23.9339994372479</v>
+        <v>23.70101408109493</v>
       </c>
       <c r="D4">
-        <v>24.3529994372479</v>
+        <v>24.36401408109493</v>
       </c>
       <c r="E4">
-        <v>0.488</v>
+        <v>0.732</v>
       </c>
       <c r="F4">
-        <v>0.488</v>
+        <v>0.732</v>
       </c>
       <c r="G4">
         <v>0.06900000000000001</v>
@@ -1603,28 +1603,28 @@
         <v>32.9</v>
       </c>
       <c r="M4">
-        <v>0.0245464</v>
+        <v>0.03681959999999999</v>
       </c>
       <c r="N4">
-        <v>32.8754536</v>
+        <v>32.8631804</v>
       </c>
       <c r="O4">
-        <v>6.57509072</v>
+        <v>6.57263608</v>
       </c>
       <c r="P4">
-        <v>26.30036288</v>
+        <v>26.29054432</v>
       </c>
       <c r="Q4">
-        <v>30.70036288</v>
+        <v>30.69054432</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1290739548547612</v>
+        <v>0.1297635085735933</v>
       </c>
       <c r="T4">
-        <v>0.9976005215049707</v>
+        <v>1.005861197375504</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>1340.318743278037</v>
+        <v>893.5458288520246</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1270778033163855</v>
+        <v>0.126858330875105</v>
       </c>
       <c r="C5">
-        <v>23.70101408109493</v>
+        <v>23.46803869310027</v>
       </c>
       <c r="D5">
-        <v>24.36401408109493</v>
+        <v>24.37503869310027</v>
       </c>
       <c r="E5">
-        <v>0.732</v>
+        <v>0.976</v>
       </c>
       <c r="F5">
-        <v>0.732</v>
+        <v>0.976</v>
       </c>
       <c r="G5">
         <v>0.06900000000000001</v>
@@ -1685,28 +1685,28 @@
         <v>32.9</v>
       </c>
       <c r="M5">
-        <v>0.03681959999999999</v>
+        <v>0.0490928</v>
       </c>
       <c r="N5">
-        <v>32.8631804</v>
+        <v>32.8509072</v>
       </c>
       <c r="O5">
-        <v>6.57263608</v>
+        <v>6.570181440000001</v>
       </c>
       <c r="P5">
-        <v>26.29054432</v>
+        <v>26.28072576</v>
       </c>
       <c r="Q5">
-        <v>30.69054432</v>
+        <v>30.68072576</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1297635085735933</v>
+        <v>0.1304674279949011</v>
       </c>
       <c r="T5">
-        <v>1.005861197375504</v>
+        <v>1.014293970660007</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>893.5458288520246</v>
+        <v>670.1593716390184</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.126858330875105</v>
+        <v>0.1266388584338246</v>
       </c>
       <c r="C6">
-        <v>23.46803869310027</v>
+        <v>23.2350732868017</v>
       </c>
       <c r="D6">
-        <v>24.37503869310027</v>
+        <v>24.3860732868017</v>
       </c>
       <c r="E6">
-        <v>0.976</v>
+        <v>1.22</v>
       </c>
       <c r="F6">
-        <v>0.976</v>
+        <v>1.22</v>
       </c>
       <c r="G6">
         <v>0.06900000000000001</v>
@@ -1767,28 +1767,28 @@
         <v>32.9</v>
       </c>
       <c r="M6">
-        <v>0.0490928</v>
+        <v>0.061366</v>
       </c>
       <c r="N6">
-        <v>32.8509072</v>
+        <v>32.838634</v>
       </c>
       <c r="O6">
-        <v>6.570181440000001</v>
+        <v>6.5677268</v>
       </c>
       <c r="P6">
-        <v>26.28072576</v>
+        <v>26.2709072</v>
       </c>
       <c r="Q6">
-        <v>30.68072576</v>
+        <v>30.6709072</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1304674279949011</v>
+        <v>0.1311861667724469</v>
       </c>
       <c r="T6">
-        <v>1.014293970660007</v>
+        <v>1.022904276013657</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>670.1593716390184</v>
+        <v>536.1274973112147</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1266388584338246</v>
+        <v>0.1264193859925441</v>
       </c>
       <c r="C7">
-        <v>23.2350732868017</v>
+        <v>23.00211787576152</v>
       </c>
       <c r="D7">
-        <v>24.3860732868017</v>
+        <v>24.39711787576152</v>
       </c>
       <c r="E7">
-        <v>1.22</v>
+        <v>1.464</v>
       </c>
       <c r="F7">
-        <v>1.22</v>
+        <v>1.464</v>
       </c>
       <c r="G7">
         <v>0.06900000000000001</v>
@@ -1849,28 +1849,28 @@
         <v>32.9</v>
       </c>
       <c r="M7">
-        <v>0.061366</v>
+        <v>0.07363919999999999</v>
       </c>
       <c r="N7">
-        <v>32.838634</v>
+        <v>32.8263608</v>
       </c>
       <c r="O7">
-        <v>6.5677268</v>
+        <v>6.565272159999999</v>
       </c>
       <c r="P7">
-        <v>26.2709072</v>
+        <v>26.26108864</v>
       </c>
       <c r="Q7">
-        <v>30.6709072</v>
+        <v>30.66108864</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1311861667724469</v>
+        <v>0.1319201978644086</v>
       </c>
       <c r="T7">
-        <v>1.022904276013657</v>
+        <v>1.031697779353556</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>536.1274973112147</v>
+        <v>446.7729144260123</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1264193859925441</v>
+        <v>0.1261999135512637</v>
       </c>
       <c r="C8">
-        <v>23.00211787576152</v>
+        <v>22.76917247356661</v>
       </c>
       <c r="D8">
-        <v>24.39711787576152</v>
+        <v>24.40817247356661</v>
       </c>
       <c r="E8">
-        <v>1.464</v>
+        <v>1.708</v>
       </c>
       <c r="F8">
-        <v>1.464</v>
+        <v>1.708</v>
       </c>
       <c r="G8">
         <v>0.06900000000000001</v>
@@ -1931,28 +1931,28 @@
         <v>32.9</v>
       </c>
       <c r="M8">
-        <v>0.07363919999999999</v>
+        <v>0.08591239999999999</v>
       </c>
       <c r="N8">
-        <v>32.8263608</v>
+        <v>32.8140876</v>
       </c>
       <c r="O8">
-        <v>6.565272159999999</v>
+        <v>6.56281752</v>
       </c>
       <c r="P8">
-        <v>26.26108864</v>
+        <v>26.25127008</v>
       </c>
       <c r="Q8">
-        <v>30.66108864</v>
+        <v>30.65127008</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1319201978644086</v>
+        <v>0.1326700145712513</v>
       </c>
       <c r="T8">
-        <v>1.031697779353556</v>
+        <v>1.040680390292161</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>446.7729144260123</v>
+        <v>382.9482123651534</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1261999135512637</v>
+        <v>0.1259804411099832</v>
       </c>
       <c r="C9">
-        <v>22.76917247356661</v>
+        <v>22.53623709382847</v>
       </c>
       <c r="D9">
-        <v>24.40817247356661</v>
+        <v>24.41923709382847</v>
       </c>
       <c r="E9">
-        <v>1.708</v>
+        <v>1.952</v>
       </c>
       <c r="F9">
-        <v>1.708</v>
+        <v>1.952</v>
       </c>
       <c r="G9">
         <v>0.06900000000000001</v>
@@ -2013,28 +2013,28 @@
         <v>32.9</v>
       </c>
       <c r="M9">
-        <v>0.0859124</v>
+        <v>0.0981856</v>
       </c>
       <c r="N9">
-        <v>32.8140876</v>
+        <v>32.8018144</v>
       </c>
       <c r="O9">
-        <v>6.56281752</v>
+        <v>6.56036288</v>
       </c>
       <c r="P9">
-        <v>26.25127008</v>
+        <v>26.24145152</v>
       </c>
       <c r="Q9">
-        <v>30.65127008</v>
+        <v>30.64145152</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1326700145712513</v>
+        <v>0.1334361316412861</v>
       </c>
       <c r="T9">
-        <v>1.040680390292161</v>
+        <v>1.049858275381606</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>382.9482123651533</v>
+        <v>335.0796858195092</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1259804411099832</v>
+        <v>0.1257609686687027</v>
       </c>
       <c r="C10">
-        <v>22.53623709382847</v>
+        <v>22.30331175018333</v>
       </c>
       <c r="D10">
-        <v>24.41923709382847</v>
+        <v>24.43031175018332</v>
       </c>
       <c r="E10">
-        <v>1.952</v>
+        <v>2.196</v>
       </c>
       <c r="F10">
-        <v>1.952</v>
+        <v>2.196</v>
       </c>
       <c r="G10">
         <v>0.06900000000000001</v>
@@ -2095,28 +2095,28 @@
         <v>32.9</v>
       </c>
       <c r="M10">
-        <v>0.0981856</v>
+        <v>0.1104588</v>
       </c>
       <c r="N10">
-        <v>32.8018144</v>
+        <v>32.7895412</v>
       </c>
       <c r="O10">
-        <v>6.56036288</v>
+        <v>6.55790824</v>
       </c>
       <c r="P10">
-        <v>26.24145152</v>
+        <v>26.23163296</v>
       </c>
       <c r="Q10">
-        <v>30.64145152</v>
+        <v>30.63163295999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1334361316412861</v>
+        <v>0.1342190864491239</v>
       </c>
       <c r="T10">
-        <v>1.049858275381606</v>
+        <v>1.059237872231259</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>335.0796858195092</v>
+        <v>297.8486096173415</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1257609686687027</v>
+        <v>0.1255414962274223</v>
       </c>
       <c r="C11">
-        <v>22.30331175018333</v>
+        <v>22.07039645629212</v>
       </c>
       <c r="D11">
-        <v>24.43031175018332</v>
+        <v>24.44139645629213</v>
       </c>
       <c r="E11">
-        <v>2.196</v>
+        <v>2.44</v>
       </c>
       <c r="F11">
-        <v>2.196</v>
+        <v>2.44</v>
       </c>
       <c r="G11">
         <v>0.06900000000000001</v>
@@ -2177,28 +2177,28 @@
         <v>32.9</v>
       </c>
       <c r="M11">
-        <v>0.1104588</v>
+        <v>0.122732</v>
       </c>
       <c r="N11">
-        <v>32.7895412</v>
+        <v>32.777268</v>
       </c>
       <c r="O11">
-        <v>6.55790824</v>
+        <v>6.5554536</v>
       </c>
       <c r="P11">
-        <v>26.23163296</v>
+        <v>26.2218144</v>
       </c>
       <c r="Q11">
-        <v>30.63163295999999</v>
+        <v>30.6218144</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1342190864491239</v>
+        <v>0.1350194402526914</v>
       </c>
       <c r="T11">
-        <v>1.059237872231259</v>
+        <v>1.068825904566459</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>297.8486096173415</v>
+        <v>268.0637486556074</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1255414962274223</v>
+        <v>0.1253220237861418</v>
       </c>
       <c r="C12">
-        <v>22.07039645629212</v>
+        <v>21.83749122584063</v>
       </c>
       <c r="D12">
-        <v>24.44139645629213</v>
+        <v>24.45249122584063</v>
       </c>
       <c r="E12">
-        <v>2.44</v>
+        <v>2.684</v>
       </c>
       <c r="F12">
-        <v>2.44</v>
+        <v>2.684</v>
       </c>
       <c r="G12">
         <v>0.06900000000000001</v>
@@ -2259,28 +2259,28 @@
         <v>32.9</v>
       </c>
       <c r="M12">
-        <v>0.122732</v>
+        <v>0.1350052</v>
       </c>
       <c r="N12">
-        <v>32.777268</v>
+        <v>32.7649948</v>
       </c>
       <c r="O12">
-        <v>6.5554536</v>
+        <v>6.55299896</v>
       </c>
       <c r="P12">
-        <v>26.2218144</v>
+        <v>26.21199584</v>
       </c>
       <c r="Q12">
-        <v>30.6218144</v>
+        <v>30.61199584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1350194402526915</v>
+        <v>0.1358377795349908</v>
       </c>
       <c r="T12">
-        <v>1.068825904566459</v>
+        <v>1.07862939830245</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>268.0637486556074</v>
+        <v>243.694316959643</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1253220237861418</v>
+        <v>0.1251025513448614</v>
       </c>
       <c r="C13">
-        <v>21.83749122584063</v>
+        <v>21.60459607253946</v>
       </c>
       <c r="D13">
-        <v>24.45249122584063</v>
+        <v>24.46359607253946</v>
       </c>
       <c r="E13">
-        <v>2.684</v>
+        <v>2.928</v>
       </c>
       <c r="F13">
-        <v>2.684</v>
+        <v>2.928</v>
       </c>
       <c r="G13">
         <v>0.06900000000000001</v>
@@ -2341,28 +2341,28 @@
         <v>32.9</v>
       </c>
       <c r="M13">
-        <v>0.1350052</v>
+        <v>0.1472784</v>
       </c>
       <c r="N13">
-        <v>32.7649948</v>
+        <v>32.7527216</v>
       </c>
       <c r="O13">
-        <v>6.55299896</v>
+        <v>6.55054432</v>
       </c>
       <c r="P13">
-        <v>26.21199584</v>
+        <v>26.20217728</v>
       </c>
       <c r="Q13">
-        <v>30.61199584</v>
+        <v>30.60217728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1358377795349908</v>
+        <v>0.1366747174373425</v>
       </c>
       <c r="T13">
-        <v>1.07862939830245</v>
+        <v>1.08865569871426</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>243.694316959643</v>
+        <v>223.3864572130062</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1251025513448614</v>
+        <v>0.1248830789035809</v>
       </c>
       <c r="C14">
-        <v>21.60459607253946</v>
+        <v>21.37171101012417</v>
       </c>
       <c r="D14">
-        <v>24.46359607253946</v>
+        <v>24.47471101012417</v>
       </c>
       <c r="E14">
-        <v>2.928</v>
+        <v>3.172</v>
       </c>
       <c r="F14">
-        <v>2.928</v>
+        <v>3.172</v>
       </c>
       <c r="G14">
         <v>0.06900000000000001</v>
@@ -2423,28 +2423,28 @@
         <v>32.9</v>
       </c>
       <c r="M14">
-        <v>0.1472784</v>
+        <v>0.1595516</v>
       </c>
       <c r="N14">
-        <v>32.7527216</v>
+        <v>32.7404484</v>
       </c>
       <c r="O14">
-        <v>6.55054432</v>
+        <v>6.54808968</v>
       </c>
       <c r="P14">
-        <v>26.20217728</v>
+        <v>26.19235872</v>
       </c>
       <c r="Q14">
-        <v>30.60217728</v>
+        <v>30.59235872</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1366747174373425</v>
+        <v>0.1375308952914723</v>
       </c>
       <c r="T14">
-        <v>1.08865569871426</v>
+        <v>1.098912488790708</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>223.3864572130062</v>
+        <v>206.2028835812364</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1248830789035809</v>
+        <v>0.1246636064623005</v>
       </c>
       <c r="C15">
-        <v>21.37171101012417</v>
+        <v>21.13883605235525</v>
       </c>
       <c r="D15">
-        <v>24.47471101012417</v>
+        <v>24.48583605235525</v>
       </c>
       <c r="E15">
-        <v>3.172</v>
+        <v>3.416</v>
       </c>
       <c r="F15">
-        <v>3.172</v>
+        <v>3.416</v>
       </c>
       <c r="G15">
         <v>0.06900000000000001</v>
@@ -2505,28 +2505,28 @@
         <v>32.9</v>
       </c>
       <c r="M15">
-        <v>0.1595516</v>
+        <v>0.1718248</v>
       </c>
       <c r="N15">
-        <v>32.7404484</v>
+        <v>32.7281752</v>
       </c>
       <c r="O15">
-        <v>6.54808968</v>
+        <v>6.54563504</v>
       </c>
       <c r="P15">
-        <v>26.19235872</v>
+        <v>26.18254015999999</v>
       </c>
       <c r="Q15">
-        <v>30.59235872</v>
+        <v>30.58254015999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1375308952914723</v>
+        <v>0.138406984258489</v>
       </c>
       <c r="T15">
-        <v>1.098912488790708</v>
+        <v>1.109407808868935</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>206.2028835812364</v>
+        <v>191.4741061825766</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1246636064623005</v>
+        <v>0.12444413402102</v>
       </c>
       <c r="C16">
-        <v>21.13883605235525</v>
+        <v>20.90597121301827</v>
       </c>
       <c r="D16">
-        <v>24.48583605235525</v>
+        <v>24.49697121301827</v>
       </c>
       <c r="E16">
-        <v>3.416</v>
+        <v>3.66</v>
       </c>
       <c r="F16">
-        <v>3.416</v>
+        <v>3.66</v>
       </c>
       <c r="G16">
         <v>0.06900000000000001</v>
@@ -2587,28 +2587,28 @@
         <v>32.9</v>
       </c>
       <c r="M16">
-        <v>0.1718248</v>
+        <v>0.184098</v>
       </c>
       <c r="N16">
-        <v>32.7281752</v>
+        <v>32.715902</v>
       </c>
       <c r="O16">
-        <v>6.54563504</v>
+        <v>6.543180400000001</v>
       </c>
       <c r="P16">
-        <v>26.18254015999999</v>
+        <v>26.1727216</v>
       </c>
       <c r="Q16">
-        <v>30.58254015999999</v>
+        <v>30.5727216</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.138406984258489</v>
+        <v>0.139303687083553</v>
       </c>
       <c r="T16">
-        <v>1.109407808868935</v>
+        <v>1.120150077654884</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>191.4741061825766</v>
+        <v>178.7091657704049</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.12444413402102</v>
+        <v>0.1242246615797396</v>
       </c>
       <c r="C17">
-        <v>20.90597121301827</v>
+        <v>20.67311650592384</v>
       </c>
       <c r="D17">
-        <v>24.49697121301827</v>
+        <v>24.50811650592384</v>
       </c>
       <c r="E17">
-        <v>3.66</v>
+        <v>3.904</v>
       </c>
       <c r="F17">
-        <v>3.66</v>
+        <v>3.904</v>
       </c>
       <c r="G17">
         <v>0.06900000000000001</v>
@@ -2669,28 +2669,28 @@
         <v>32.9</v>
       </c>
       <c r="M17">
-        <v>0.184098</v>
+        <v>0.1963712</v>
       </c>
       <c r="N17">
-        <v>32.715902</v>
+        <v>32.7036288</v>
       </c>
       <c r="O17">
-        <v>6.543180400000001</v>
+        <v>6.54072576</v>
       </c>
       <c r="P17">
-        <v>26.1727216</v>
+        <v>26.16290304</v>
       </c>
       <c r="Q17">
-        <v>30.5727216</v>
+        <v>30.56290303999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.139303687083553</v>
+        <v>0.1402217399758804</v>
       </c>
       <c r="T17">
-        <v>1.120150077654884</v>
+        <v>1.131148114745261</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>178.7091657704049</v>
+        <v>167.5398429097546</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1242246615797396</v>
+        <v>0.1240051891384591</v>
       </c>
       <c r="C18">
-        <v>20.67311650592384</v>
+        <v>20.44027194490774</v>
       </c>
       <c r="D18">
-        <v>24.50811650592384</v>
+        <v>24.51927194490774</v>
       </c>
       <c r="E18">
-        <v>3.904</v>
+        <v>4.148</v>
       </c>
       <c r="F18">
-        <v>3.904</v>
+        <v>4.148</v>
       </c>
       <c r="G18">
         <v>0.06900000000000001</v>
@@ -2751,28 +2751,28 @@
         <v>32.9</v>
       </c>
       <c r="M18">
-        <v>0.1963712</v>
+        <v>0.2086444</v>
       </c>
       <c r="N18">
-        <v>32.7036288</v>
+        <v>32.6913556</v>
       </c>
       <c r="O18">
-        <v>6.54072576</v>
+        <v>6.538271120000001</v>
       </c>
       <c r="P18">
-        <v>26.16290304</v>
+        <v>26.15308448</v>
       </c>
       <c r="Q18">
-        <v>30.56290303999999</v>
+        <v>30.55308448</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1402217399758804</v>
+        <v>0.1411619146246496</v>
       </c>
       <c r="T18">
-        <v>1.131148114745261</v>
+        <v>1.142411164777575</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>167.5398429097546</v>
+        <v>157.6845580327102</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1240051891384591</v>
+        <v>0.1237857166971787</v>
       </c>
       <c r="C19">
-        <v>20.44027194490774</v>
+        <v>20.20743754383096</v>
       </c>
       <c r="D19">
-        <v>24.51927194490774</v>
+        <v>24.53043754383096</v>
       </c>
       <c r="E19">
-        <v>4.148</v>
+        <v>4.392</v>
       </c>
       <c r="F19">
-        <v>4.148</v>
+        <v>4.392</v>
       </c>
       <c r="G19">
         <v>0.06900000000000001</v>
@@ -2833,28 +2833,28 @@
         <v>32.9</v>
       </c>
       <c r="M19">
-        <v>0.2086444</v>
+        <v>0.2209176</v>
       </c>
       <c r="N19">
-        <v>32.6913556</v>
+        <v>32.6790824</v>
       </c>
       <c r="O19">
-        <v>6.538271120000001</v>
+        <v>6.53581648</v>
       </c>
       <c r="P19">
-        <v>26.15308448</v>
+        <v>26.14326592</v>
       </c>
       <c r="Q19">
-        <v>30.55308448</v>
+        <v>30.54326592</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1411619146246496</v>
+        <v>0.142125020362413</v>
       </c>
       <c r="T19">
-        <v>1.142411164777575</v>
+        <v>1.153948923347262</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>157.6845580327102</v>
+        <v>148.9243048086707</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1237857166971787</v>
+        <v>0.1235662442558982</v>
       </c>
       <c r="C20">
-        <v>20.20743754383096</v>
+        <v>19.97461331657973</v>
       </c>
       <c r="D20">
-        <v>24.53043754383096</v>
+        <v>24.54161331657973</v>
       </c>
       <c r="E20">
-        <v>4.391999999999999</v>
+        <v>4.636</v>
       </c>
       <c r="F20">
-        <v>4.391999999999999</v>
+        <v>4.636</v>
       </c>
       <c r="G20">
         <v>0.06900000000000001</v>
@@ -2915,28 +2915,28 @@
         <v>32.9</v>
       </c>
       <c r="M20">
-        <v>0.2209176</v>
+        <v>0.2331908</v>
       </c>
       <c r="N20">
-        <v>32.6790824</v>
+        <v>32.6668092</v>
       </c>
       <c r="O20">
-        <v>6.53581648</v>
+        <v>6.53336184</v>
       </c>
       <c r="P20">
-        <v>26.14326592</v>
+        <v>26.13344736</v>
       </c>
       <c r="Q20">
-        <v>30.54326592</v>
+        <v>30.53344736</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.142125020362413</v>
+        <v>0.1431119064887632</v>
       </c>
       <c r="T20">
-        <v>1.153948923347262</v>
+        <v>1.165771564844596</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>148.9243048086708</v>
+        <v>141.0861835029512</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1235662442558982</v>
+        <v>0.1233467718146178</v>
       </c>
       <c r="C21">
-        <v>19.97461331657973</v>
+        <v>19.74179927706562</v>
       </c>
       <c r="D21">
-        <v>24.54161331657973</v>
+        <v>24.55279927706562</v>
       </c>
       <c r="E21">
-        <v>4.636</v>
+        <v>4.88</v>
       </c>
       <c r="F21">
-        <v>4.636</v>
+        <v>4.88</v>
       </c>
       <c r="G21">
         <v>0.06900000000000001</v>
@@ -2997,28 +2997,28 @@
         <v>32.9</v>
       </c>
       <c r="M21">
-        <v>0.2331908</v>
+        <v>0.245464</v>
       </c>
       <c r="N21">
-        <v>32.6668092</v>
+        <v>32.654536</v>
       </c>
       <c r="O21">
-        <v>6.53336184</v>
+        <v>6.530907200000001</v>
       </c>
       <c r="P21">
-        <v>26.13344736</v>
+        <v>26.1236288</v>
       </c>
       <c r="Q21">
-        <v>30.53344736</v>
+        <v>30.5236288</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1431119064887632</v>
+        <v>0.1441234647682722</v>
       </c>
       <c r="T21">
-        <v>1.165771564844596</v>
+        <v>1.177889772379363</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>141.0861835029512</v>
+        <v>134.0318743278037</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1233467718146178</v>
+        <v>0.1231272993733373</v>
       </c>
       <c r="C22">
-        <v>19.74179927706562</v>
+        <v>19.50899543922554</v>
       </c>
       <c r="D22">
-        <v>24.55279927706562</v>
+        <v>24.56399543922555</v>
       </c>
       <c r="E22">
-        <v>4.88</v>
+        <v>5.124000000000001</v>
       </c>
       <c r="F22">
-        <v>4.88</v>
+        <v>5.124000000000001</v>
       </c>
       <c r="G22">
         <v>0.06900000000000001</v>
@@ -3079,28 +3079,28 @@
         <v>32.9</v>
       </c>
       <c r="M22">
-        <v>0.245464</v>
+        <v>0.2577372</v>
       </c>
       <c r="N22">
-        <v>32.654536</v>
+        <v>32.6422628</v>
       </c>
       <c r="O22">
-        <v>6.530907200000001</v>
+        <v>6.52845256</v>
       </c>
       <c r="P22">
-        <v>26.1236288</v>
+        <v>26.11381024</v>
       </c>
       <c r="Q22">
-        <v>30.5236288</v>
+        <v>30.51381024</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1441234647682722</v>
+        <v>0.1451606321181485</v>
       </c>
       <c r="T22">
-        <v>1.177889772379363</v>
+        <v>1.190314769978301</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>134.0318743278037</v>
+        <v>127.6494041217178</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1231272993733373</v>
+        <v>0.1229078269320569</v>
       </c>
       <c r="C23">
-        <v>19.50899543922555</v>
+        <v>19.27620181702188</v>
       </c>
       <c r="D23">
-        <v>24.56399543922555</v>
+        <v>24.57520181702188</v>
       </c>
       <c r="E23">
-        <v>5.124</v>
+        <v>5.367999999999999</v>
       </c>
       <c r="F23">
-        <v>5.124</v>
+        <v>5.367999999999999</v>
       </c>
       <c r="G23">
         <v>0.06900000000000001</v>
@@ -3161,28 +3161,28 @@
         <v>32.9</v>
       </c>
       <c r="M23">
-        <v>0.2577371999999999</v>
+        <v>0.2700104</v>
       </c>
       <c r="N23">
-        <v>32.6422628</v>
+        <v>32.6299896</v>
       </c>
       <c r="O23">
-        <v>6.52845256</v>
+        <v>6.525997920000001</v>
       </c>
       <c r="P23">
-        <v>26.11381024</v>
+        <v>26.10399168</v>
       </c>
       <c r="Q23">
-        <v>30.51381024</v>
+        <v>30.50399168</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1451606321181485</v>
+        <v>0.146224393502637</v>
       </c>
       <c r="T23">
-        <v>1.190314769978301</v>
+        <v>1.203058357259264</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>127.6494041217178</v>
+        <v>121.8471584798215</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1229078269320569</v>
+        <v>0.1226883544907764</v>
       </c>
       <c r="C24">
-        <v>19.27620181702188</v>
+        <v>19.04341842444246</v>
       </c>
       <c r="D24">
-        <v>24.57520181702188</v>
+        <v>24.58641842444247</v>
       </c>
       <c r="E24">
-        <v>5.367999999999999</v>
+        <v>5.612</v>
       </c>
       <c r="F24">
-        <v>5.367999999999999</v>
+        <v>5.612</v>
       </c>
       <c r="G24">
         <v>0.06900000000000001</v>
@@ -3243,28 +3243,28 @@
         <v>32.9</v>
       </c>
       <c r="M24">
-        <v>0.2700104</v>
+        <v>0.2822836</v>
       </c>
       <c r="N24">
-        <v>32.6299896</v>
+        <v>32.6177164</v>
       </c>
       <c r="O24">
-        <v>6.525997920000001</v>
+        <v>6.52354328</v>
       </c>
       <c r="P24">
-        <v>26.10399168</v>
+        <v>26.09417312</v>
       </c>
       <c r="Q24">
-        <v>30.50399168</v>
+        <v>30.49417312</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.146224393502637</v>
+        <v>0.1473157850529564</v>
       </c>
       <c r="T24">
-        <v>1.203058357259264</v>
+        <v>1.216132946807264</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>121.8471584798215</v>
+        <v>116.5494559372206</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1226883544907764</v>
+        <v>0.122468882049496</v>
       </c>
       <c r="C25">
-        <v>19.04341842444246</v>
+        <v>18.81064527550073</v>
       </c>
       <c r="D25">
-        <v>24.58641842444247</v>
+        <v>24.59764527550072</v>
       </c>
       <c r="E25">
-        <v>5.612</v>
+        <v>5.856</v>
       </c>
       <c r="F25">
-        <v>5.612</v>
+        <v>5.856</v>
       </c>
       <c r="G25">
         <v>0.06900000000000001</v>
@@ -3325,28 +3325,28 @@
         <v>32.9</v>
       </c>
       <c r="M25">
-        <v>0.2822836</v>
+        <v>0.2945568</v>
       </c>
       <c r="N25">
-        <v>32.6177164</v>
+        <v>32.6054432</v>
       </c>
       <c r="O25">
-        <v>6.52354328</v>
+        <v>6.521088639999999</v>
       </c>
       <c r="P25">
-        <v>26.09417312</v>
+        <v>26.08435456</v>
       </c>
       <c r="Q25">
-        <v>30.49417312</v>
+        <v>30.48435456</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1473157850529564</v>
+        <v>0.1484358974335473</v>
       </c>
       <c r="T25">
-        <v>1.216132946807264</v>
+        <v>1.229551604501265</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>116.5494559372206</v>
+        <v>111.6932286065031</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.122468882049496</v>
+        <v>0.1222494096082155</v>
       </c>
       <c r="C26">
-        <v>18.81064527550073</v>
+        <v>18.57788238423565</v>
       </c>
       <c r="D26">
-        <v>24.59764527550072</v>
+        <v>24.60888238423565</v>
       </c>
       <c r="E26">
-        <v>5.856</v>
+        <v>6.1</v>
       </c>
       <c r="F26">
-        <v>5.856</v>
+        <v>6.1</v>
       </c>
       <c r="G26">
         <v>0.06900000000000001</v>
@@ -3407,28 +3407,28 @@
         <v>32.9</v>
       </c>
       <c r="M26">
-        <v>0.2945568</v>
+        <v>0.30683</v>
       </c>
       <c r="N26">
-        <v>32.6054432</v>
+        <v>32.59317</v>
       </c>
       <c r="O26">
-        <v>6.521088639999999</v>
+        <v>6.518634</v>
       </c>
       <c r="P26">
-        <v>26.08435456</v>
+        <v>26.074536</v>
       </c>
       <c r="Q26">
-        <v>30.48435456</v>
+        <v>30.474536</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1484358974335473</v>
+        <v>0.1495858794776207</v>
       </c>
       <c r="T26">
-        <v>1.229551604501265</v>
+        <v>1.243328093067105</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>111.6932286065031</v>
+        <v>107.2254994622429</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1222494096082155</v>
+        <v>0.122029937166935</v>
       </c>
       <c r="C27">
-        <v>18.57788238423565</v>
+        <v>18.34512976471193</v>
       </c>
       <c r="D27">
-        <v>24.60888238423565</v>
+        <v>24.62012976471193</v>
       </c>
       <c r="E27">
-        <v>6.1</v>
+        <v>6.343999999999999</v>
       </c>
       <c r="F27">
-        <v>6.1</v>
+        <v>6.343999999999999</v>
       </c>
       <c r="G27">
         <v>0.06900000000000001</v>
@@ -3489,28 +3489,28 @@
         <v>32.9</v>
       </c>
       <c r="M27">
-        <v>0.30683</v>
+        <v>0.3191032</v>
       </c>
       <c r="N27">
-        <v>32.59317</v>
+        <v>32.5808968</v>
       </c>
       <c r="O27">
-        <v>6.518634</v>
+        <v>6.51617936</v>
       </c>
       <c r="P27">
-        <v>26.074536</v>
+        <v>26.06471744</v>
       </c>
       <c r="Q27">
-        <v>30.474536</v>
+        <v>30.46471744</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1495858794776207</v>
+        <v>0.1507669421174798</v>
       </c>
       <c r="T27">
-        <v>1.243328093067105</v>
+        <v>1.257476919161752</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>107.2254994622429</v>
+        <v>103.1014417906182</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.122029937166935</v>
+        <v>0.1218104647256546</v>
       </c>
       <c r="C28">
-        <v>18.34512976471193</v>
+        <v>18.11238743101996</v>
       </c>
       <c r="D28">
-        <v>24.62012976471193</v>
+        <v>24.63138743101997</v>
       </c>
       <c r="E28">
-        <v>6.343999999999999</v>
+        <v>6.588</v>
       </c>
       <c r="F28">
-        <v>6.343999999999999</v>
+        <v>6.588</v>
       </c>
       <c r="G28">
         <v>0.06900000000000001</v>
@@ -3571,28 +3571,28 @@
         <v>32.9</v>
       </c>
       <c r="M28">
-        <v>0.3191032</v>
+        <v>0.3313764</v>
       </c>
       <c r="N28">
-        <v>32.5808968</v>
+        <v>32.5686236</v>
       </c>
       <c r="O28">
-        <v>6.51617936</v>
+        <v>6.513724719999999</v>
       </c>
       <c r="P28">
-        <v>26.06471744</v>
+        <v>26.05489888</v>
       </c>
       <c r="Q28">
-        <v>30.46471744</v>
+        <v>30.45489887999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1507669421174798</v>
+        <v>0.151980362637883</v>
       </c>
       <c r="T28">
-        <v>1.257476919161752</v>
+        <v>1.272013384327486</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>103.1014417906182</v>
+        <v>99.28286987244716</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1218104647256546</v>
+        <v>0.1215909922843742</v>
       </c>
       <c r="C29">
-        <v>18.11238743101996</v>
+        <v>17.87965539727593</v>
       </c>
       <c r="D29">
-        <v>24.63138743101997</v>
+        <v>24.64265539727593</v>
       </c>
       <c r="E29">
-        <v>6.588</v>
+        <v>6.832</v>
       </c>
       <c r="F29">
-        <v>6.588</v>
+        <v>6.832</v>
       </c>
       <c r="G29">
         <v>0.06900000000000001</v>
@@ -3653,28 +3653,28 @@
         <v>32.9</v>
       </c>
       <c r="M29">
-        <v>0.3313764</v>
+        <v>0.3436496</v>
       </c>
       <c r="N29">
-        <v>32.5686236</v>
+        <v>32.5563504</v>
       </c>
       <c r="O29">
-        <v>6.513724719999999</v>
+        <v>6.51127008</v>
       </c>
       <c r="P29">
-        <v>26.05489888</v>
+        <v>26.04508032</v>
       </c>
       <c r="Q29">
-        <v>30.45489887999999</v>
+        <v>30.44508032</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.151980362637883</v>
+        <v>0.153227489283853</v>
       </c>
       <c r="T29">
-        <v>1.272013384327486</v>
+        <v>1.286953640192267</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>99.28286987244716</v>
+        <v>95.73705309128833</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1215909922843742</v>
+        <v>0.1213715198430937</v>
       </c>
       <c r="C30">
-        <v>17.87965539727593</v>
+        <v>17.64693367762187</v>
       </c>
       <c r="D30">
-        <v>24.64265539727593</v>
+        <v>24.65393367762187</v>
       </c>
       <c r="E30">
-        <v>6.832</v>
+        <v>7.076000000000001</v>
       </c>
       <c r="F30">
-        <v>6.832</v>
+        <v>7.076000000000001</v>
       </c>
       <c r="G30">
         <v>0.06900000000000001</v>
@@ -3735,28 +3735,28 @@
         <v>32.9</v>
       </c>
       <c r="M30">
-        <v>0.3436496</v>
+        <v>0.3559228</v>
       </c>
       <c r="N30">
-        <v>32.5563504</v>
+        <v>32.5440772</v>
       </c>
       <c r="O30">
-        <v>6.51127008</v>
+        <v>6.508815439999999</v>
       </c>
       <c r="P30">
-        <v>26.04508032</v>
+        <v>26.03526176</v>
       </c>
       <c r="Q30">
-        <v>30.44508032</v>
+        <v>30.43526176</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.153227489283853</v>
+        <v>0.1545097462578784</v>
       </c>
       <c r="T30">
-        <v>1.286953640192267</v>
+        <v>1.30231474833493</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>95.73705309128833</v>
+        <v>92.43577539848529</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1213715198430937</v>
+        <v>0.1211520474018132</v>
       </c>
       <c r="C31">
-        <v>17.64693367762187</v>
+        <v>17.41422228622569</v>
       </c>
       <c r="D31">
-        <v>24.65393367762187</v>
+        <v>24.6652222862257</v>
       </c>
       <c r="E31">
-        <v>7.075999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="F31">
-        <v>7.075999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="G31">
         <v>0.06900000000000001</v>
@@ -3817,28 +3817,28 @@
         <v>32.9</v>
       </c>
       <c r="M31">
-        <v>0.3559227999999999</v>
+        <v>0.368196</v>
       </c>
       <c r="N31">
-        <v>32.5440772</v>
+        <v>32.531804</v>
       </c>
       <c r="O31">
-        <v>6.508815439999999</v>
+        <v>6.5063608</v>
       </c>
       <c r="P31">
-        <v>26.03526176</v>
+        <v>26.0254432</v>
       </c>
       <c r="Q31">
-        <v>30.43526176</v>
+        <v>30.4254432</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1545097462578784</v>
+        <v>0.1558286391454475</v>
       </c>
       <c r="T31">
-        <v>1.30231474833493</v>
+        <v>1.318114745281668</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>92.4357753984853</v>
+        <v>89.35458288520246</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1211520474018132</v>
+        <v>0.1209325749605328</v>
       </c>
       <c r="C32">
-        <v>17.41422228622569</v>
+        <v>17.18152123728131</v>
       </c>
       <c r="D32">
-        <v>24.6652222862257</v>
+        <v>24.67652123728131</v>
       </c>
       <c r="E32">
-        <v>7.319999999999999</v>
+        <v>7.563999999999999</v>
       </c>
       <c r="F32">
-        <v>7.319999999999999</v>
+        <v>7.563999999999999</v>
       </c>
       <c r="G32">
         <v>0.06900000000000001</v>
@@ -3899,28 +3899,28 @@
         <v>32.9</v>
       </c>
       <c r="M32">
-        <v>0.368196</v>
+        <v>0.3804692</v>
       </c>
       <c r="N32">
-        <v>32.531804</v>
+        <v>32.5195308</v>
       </c>
       <c r="O32">
-        <v>6.5063608</v>
+        <v>6.50390616</v>
       </c>
       <c r="P32">
-        <v>26.0254432</v>
+        <v>26.01562464</v>
       </c>
       <c r="Q32">
-        <v>30.4254432</v>
+        <v>30.41562464</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1558286391454475</v>
+        <v>0.1571857608123663</v>
       </c>
       <c r="T32">
-        <v>1.318114745281668</v>
+        <v>1.334372713154399</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>89.35458288520246</v>
+        <v>86.47217698567979</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1209325749605328</v>
+        <v>0.1207131025192523</v>
       </c>
       <c r="C33">
-        <v>17.18152123728131</v>
+        <v>16.9488305450086</v>
       </c>
       <c r="D33">
-        <v>24.67652123728131</v>
+        <v>24.68783054500861</v>
       </c>
       <c r="E33">
-        <v>7.563999999999999</v>
+        <v>7.808</v>
       </c>
       <c r="F33">
-        <v>7.563999999999999</v>
+        <v>7.808</v>
       </c>
       <c r="G33">
         <v>0.06900000000000001</v>
@@ -3981,28 +3981,28 @@
         <v>32.9</v>
       </c>
       <c r="M33">
-        <v>0.3804692</v>
+        <v>0.3927424</v>
       </c>
       <c r="N33">
-        <v>32.5195308</v>
+        <v>32.5072576</v>
       </c>
       <c r="O33">
-        <v>6.50390616</v>
+        <v>6.50145152</v>
       </c>
       <c r="P33">
-        <v>26.01562464</v>
+        <v>26.00580608</v>
       </c>
       <c r="Q33">
-        <v>30.41562464</v>
+        <v>30.40580607999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1571857608123663</v>
+        <v>0.1585827978224299</v>
       </c>
       <c r="T33">
-        <v>1.334372713154399</v>
+        <v>1.351108856552799</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>86.47217698567979</v>
+        <v>83.76992145487728</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1207131025192523</v>
+        <v>0.1204936300779719</v>
       </c>
       <c r="C34">
-        <v>16.9488305450086</v>
+        <v>16.71615022365359</v>
       </c>
       <c r="D34">
-        <v>24.68783054500861</v>
+        <v>24.69915022365359</v>
       </c>
       <c r="E34">
-        <v>7.808</v>
+        <v>8.052</v>
       </c>
       <c r="F34">
-        <v>7.808</v>
+        <v>8.052</v>
       </c>
       <c r="G34">
         <v>0.06900000000000001</v>
@@ -4063,28 +4063,28 @@
         <v>32.9</v>
       </c>
       <c r="M34">
-        <v>0.3927424</v>
+        <v>0.4050156</v>
       </c>
       <c r="N34">
-        <v>32.5072576</v>
+        <v>32.4949844</v>
       </c>
       <c r="O34">
-        <v>6.50145152</v>
+        <v>6.49899688</v>
       </c>
       <c r="P34">
-        <v>26.00580608</v>
+        <v>25.99598752</v>
       </c>
       <c r="Q34">
-        <v>30.40580607999999</v>
+        <v>30.39598752</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1585827978224299</v>
+        <v>0.1600215374298088</v>
       </c>
       <c r="T34">
-        <v>1.351108856552799</v>
+        <v>1.3683445863213</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>83.76992145487728</v>
+        <v>81.23143898654769</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1204936300779719</v>
+        <v>0.1202741576366914</v>
       </c>
       <c r="C35">
-        <v>16.71615022365359</v>
+        <v>16.48348028748839</v>
       </c>
       <c r="D35">
-        <v>24.69915022365359</v>
+        <v>24.71048028748839</v>
       </c>
       <c r="E35">
-        <v>8.052</v>
+        <v>8.295999999999999</v>
       </c>
       <c r="F35">
-        <v>8.052</v>
+        <v>8.295999999999999</v>
       </c>
       <c r="G35">
         <v>0.06900000000000001</v>
@@ -4145,28 +4145,28 @@
         <v>32.9</v>
       </c>
       <c r="M35">
-        <v>0.4050156</v>
+        <v>0.4172888</v>
       </c>
       <c r="N35">
-        <v>32.4949844</v>
+        <v>32.4827112</v>
       </c>
       <c r="O35">
-        <v>6.49899688</v>
+        <v>6.49654224</v>
       </c>
       <c r="P35">
-        <v>25.99598752</v>
+        <v>25.98616896</v>
       </c>
       <c r="Q35">
-        <v>30.39598752</v>
+        <v>30.38616896</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1600215374298088</v>
+        <v>0.1615038752071082</v>
       </c>
       <c r="T35">
-        <v>1.3683445863213</v>
+        <v>1.386102610931271</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>81.23143898654769</v>
+        <v>78.84227901635511</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1202741576366914</v>
+        <v>0.120054685195411</v>
       </c>
       <c r="C36">
-        <v>16.48348028748839</v>
+        <v>16.25082075081133</v>
       </c>
       <c r="D36">
-        <v>24.71048028748839</v>
+        <v>24.72182075081133</v>
       </c>
       <c r="E36">
-        <v>8.295999999999999</v>
+        <v>8.540000000000001</v>
       </c>
       <c r="F36">
-        <v>8.295999999999999</v>
+        <v>8.540000000000001</v>
       </c>
       <c r="G36">
         <v>0.06900000000000001</v>
@@ -4227,28 +4227,28 @@
         <v>32.9</v>
       </c>
       <c r="M36">
-        <v>0.4172888</v>
+        <v>0.429562</v>
       </c>
       <c r="N36">
-        <v>32.4827112</v>
+        <v>32.470438</v>
       </c>
       <c r="O36">
-        <v>6.49654224</v>
+        <v>6.4940876</v>
       </c>
       <c r="P36">
-        <v>25.98616896</v>
+        <v>25.9763504</v>
       </c>
       <c r="Q36">
-        <v>30.38616896</v>
+        <v>30.3763504</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1615038752071082</v>
+        <v>0.1630318233775553</v>
       </c>
       <c r="T36">
-        <v>1.386102610931271</v>
+        <v>1.404407036298471</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>78.84227901635511</v>
+        <v>76.58964247303068</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.120054685195411</v>
+        <v>0.1198352127541305</v>
       </c>
       <c r="C37">
-        <v>16.25082075081133</v>
+        <v>16.018171627947</v>
       </c>
       <c r="D37">
-        <v>24.72182075081133</v>
+        <v>24.733171627947</v>
       </c>
       <c r="E37">
-        <v>8.540000000000001</v>
+        <v>8.784000000000001</v>
       </c>
       <c r="F37">
-        <v>8.540000000000001</v>
+        <v>8.784000000000001</v>
       </c>
       <c r="G37">
         <v>0.06900000000000001</v>
@@ -4309,28 +4309,28 @@
         <v>32.9</v>
       </c>
       <c r="M37">
-        <v>0.429562</v>
+        <v>0.4418352</v>
       </c>
       <c r="N37">
-        <v>32.470438</v>
+        <v>32.4581648</v>
       </c>
       <c r="O37">
-        <v>6.4940876</v>
+        <v>6.49163296</v>
       </c>
       <c r="P37">
-        <v>25.9763504</v>
+        <v>25.96653184</v>
       </c>
       <c r="Q37">
-        <v>30.3763504</v>
+        <v>30.36653184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1630318233775553</v>
+        <v>0.1646075199283289</v>
       </c>
       <c r="T37">
-        <v>1.404407036298471</v>
+        <v>1.423283474958397</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>76.58964247303068</v>
+        <v>74.46215240433536</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1198352127541305</v>
+        <v>0.11961574031285</v>
       </c>
       <c r="C38">
-        <v>16.018171627947</v>
+        <v>15.78553293324631</v>
       </c>
       <c r="D38">
-        <v>24.733171627947</v>
+        <v>24.74453293324631</v>
       </c>
       <c r="E38">
-        <v>8.783999999999999</v>
+        <v>9.027999999999999</v>
       </c>
       <c r="F38">
-        <v>8.783999999999999</v>
+        <v>9.027999999999999</v>
       </c>
       <c r="G38">
         <v>0.06900000000000001</v>
@@ -4391,28 +4391,28 @@
         <v>32.9</v>
       </c>
       <c r="M38">
-        <v>0.4418351999999999</v>
+        <v>0.4541083999999999</v>
       </c>
       <c r="N38">
-        <v>32.4581648</v>
+        <v>32.4458916</v>
       </c>
       <c r="O38">
-        <v>6.49163296</v>
+        <v>6.48917832</v>
       </c>
       <c r="P38">
-        <v>25.96653184</v>
+        <v>25.95671328</v>
       </c>
       <c r="Q38">
-        <v>30.36653184</v>
+        <v>30.35671327999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1646075199283289</v>
+        <v>0.1662332385918255</v>
       </c>
       <c r="T38">
-        <v>1.423283474958397</v>
+        <v>1.442759165639273</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>74.46215240433538</v>
+        <v>72.4496617988128</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.11961574031285</v>
+        <v>0.1193962678715696</v>
       </c>
       <c r="C39">
-        <v>15.78553293324631</v>
+        <v>15.55290468108655</v>
       </c>
       <c r="D39">
-        <v>24.74453293324631</v>
+        <v>24.75590468108656</v>
       </c>
       <c r="E39">
-        <v>9.027999999999999</v>
+        <v>9.272</v>
       </c>
       <c r="F39">
-        <v>9.027999999999999</v>
+        <v>9.272</v>
       </c>
       <c r="G39">
         <v>0.06900000000000001</v>
@@ -4473,28 +4473,28 @@
         <v>32.9</v>
       </c>
       <c r="M39">
-        <v>0.4541083999999999</v>
+        <v>0.4663816</v>
       </c>
       <c r="N39">
-        <v>32.4458916</v>
+        <v>32.4336184</v>
       </c>
       <c r="O39">
-        <v>6.48917832</v>
+        <v>6.486723680000001</v>
       </c>
       <c r="P39">
-        <v>25.95671328</v>
+        <v>25.94689472</v>
       </c>
       <c r="Q39">
-        <v>30.35671327999999</v>
+        <v>30.34689472</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1662332385918255</v>
+        <v>0.1679113997928542</v>
       </c>
       <c r="T39">
-        <v>1.442759165639273</v>
+        <v>1.462863104406628</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>72.4496617988128</v>
+        <v>70.54309175147561</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1193962678715696</v>
+        <v>0.1191767954302892</v>
       </c>
       <c r="C40">
-        <v>15.55290468108655</v>
+        <v>15.32028688587146</v>
       </c>
       <c r="D40">
-        <v>24.75590468108656</v>
+        <v>24.76728688587146</v>
       </c>
       <c r="E40">
-        <v>9.272</v>
+        <v>9.516</v>
       </c>
       <c r="F40">
-        <v>9.272</v>
+        <v>9.516</v>
       </c>
       <c r="G40">
         <v>0.06900000000000001</v>
@@ -4555,28 +4555,28 @@
         <v>32.9</v>
       </c>
       <c r="M40">
-        <v>0.4663816</v>
+        <v>0.4786548</v>
       </c>
       <c r="N40">
-        <v>32.4336184</v>
+        <v>32.4213452</v>
       </c>
       <c r="O40">
-        <v>6.486723680000001</v>
+        <v>6.48426904</v>
       </c>
       <c r="P40">
-        <v>25.94689472</v>
+        <v>25.93707616</v>
       </c>
       <c r="Q40">
-        <v>30.34689472</v>
+        <v>30.33707616</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1679113997928542</v>
+        <v>0.1696445826726052</v>
       </c>
       <c r="T40">
-        <v>1.462863104406628</v>
+        <v>1.48362618870734</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>70.54309175147561</v>
+        <v>68.7342945270788</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1191767954302892</v>
+        <v>0.1189573229890087</v>
       </c>
       <c r="C41">
-        <v>15.32028688587146</v>
+        <v>15.08767956203127</v>
       </c>
       <c r="D41">
-        <v>24.76728688587146</v>
+        <v>24.77867956203127</v>
       </c>
       <c r="E41">
-        <v>9.516</v>
+        <v>9.76</v>
       </c>
       <c r="F41">
-        <v>9.516</v>
+        <v>9.76</v>
       </c>
       <c r="G41">
         <v>0.06900000000000001</v>
@@ -4637,28 +4637,28 @@
         <v>32.9</v>
       </c>
       <c r="M41">
-        <v>0.4786548</v>
+        <v>0.490928</v>
       </c>
       <c r="N41">
-        <v>32.4213452</v>
+        <v>32.409072</v>
       </c>
       <c r="O41">
-        <v>6.48426904</v>
+        <v>6.481814400000001</v>
       </c>
       <c r="P41">
-        <v>25.93707616</v>
+        <v>25.9272576</v>
       </c>
       <c r="Q41">
-        <v>30.33707616</v>
+        <v>30.3272576</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1696445826726052</v>
+        <v>0.1714355383150145</v>
       </c>
       <c r="T41">
-        <v>1.48362618870734</v>
+        <v>1.505081375818075</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>68.7342945270788</v>
+        <v>67.01593716390184</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1189573229890087</v>
+        <v>0.1187378505477282</v>
       </c>
       <c r="C42">
-        <v>15.08767956203127</v>
+        <v>14.85508272402277</v>
       </c>
       <c r="D42">
-        <v>24.77867956203127</v>
+        <v>24.79008272402277</v>
       </c>
       <c r="E42">
-        <v>9.76</v>
+        <v>10.004</v>
       </c>
       <c r="F42">
-        <v>9.76</v>
+        <v>10.004</v>
       </c>
       <c r="G42">
         <v>0.06900000000000001</v>
@@ -4719,28 +4719,28 @@
         <v>32.9</v>
       </c>
       <c r="M42">
-        <v>0.490928</v>
+        <v>0.5032011999999999</v>
       </c>
       <c r="N42">
-        <v>32.409072</v>
+        <v>32.3967988</v>
       </c>
       <c r="O42">
-        <v>6.481814400000001</v>
+        <v>6.47935976</v>
       </c>
       <c r="P42">
-        <v>25.9272576</v>
+        <v>25.91743904</v>
       </c>
       <c r="Q42">
-        <v>30.3272576</v>
+        <v>30.31743904</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1714355383150145</v>
+        <v>0.1732872043181835</v>
       </c>
       <c r="T42">
-        <v>1.505081375818075</v>
+        <v>1.52726385740714</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>67.01593716390184</v>
+        <v>65.38140211112375</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1187378505477282</v>
+        <v>0.1185183781064478</v>
       </c>
       <c r="C43">
-        <v>14.85508272402277</v>
+        <v>14.62249638632939</v>
       </c>
       <c r="D43">
-        <v>24.79008272402277</v>
+        <v>24.80149638632939</v>
       </c>
       <c r="E43">
-        <v>10.004</v>
+        <v>10.248</v>
       </c>
       <c r="F43">
-        <v>10.004</v>
+        <v>10.248</v>
       </c>
       <c r="G43">
         <v>0.06900000000000001</v>
@@ -4801,28 +4801,28 @@
         <v>32.9</v>
       </c>
       <c r="M43">
-        <v>0.5032011999999999</v>
+        <v>0.5154744</v>
       </c>
       <c r="N43">
-        <v>32.3967988</v>
+        <v>32.3845256</v>
       </c>
       <c r="O43">
-        <v>6.47935976</v>
+        <v>6.47690512</v>
       </c>
       <c r="P43">
-        <v>25.91743904</v>
+        <v>25.90762048</v>
       </c>
       <c r="Q43">
-        <v>30.31743904</v>
+        <v>30.30762048</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1732872043181835</v>
+        <v>0.1752027208731859</v>
       </c>
       <c r="T43">
-        <v>1.52726385740714</v>
+        <v>1.550211252154449</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>65.38140211112375</v>
+        <v>63.82470206085888</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1185183781064478</v>
+        <v>0.1182989056651673</v>
       </c>
       <c r="C44">
-        <v>14.62249638632939</v>
+        <v>14.38992056346123</v>
       </c>
       <c r="D44">
-        <v>24.80149638632939</v>
+        <v>24.81292056346123</v>
       </c>
       <c r="E44">
-        <v>10.248</v>
+        <v>10.492</v>
       </c>
       <c r="F44">
-        <v>10.248</v>
+        <v>10.492</v>
       </c>
       <c r="G44">
         <v>0.06900000000000001</v>
@@ -4883,28 +4883,28 @@
         <v>32.9</v>
       </c>
       <c r="M44">
-        <v>0.5154743999999999</v>
+        <v>0.5277476</v>
       </c>
       <c r="N44">
-        <v>32.3845256</v>
+        <v>32.3722524</v>
       </c>
       <c r="O44">
-        <v>6.47690512</v>
+        <v>6.474450480000001</v>
       </c>
       <c r="P44">
-        <v>25.90762048</v>
+        <v>25.89780192</v>
       </c>
       <c r="Q44">
-        <v>30.30762048</v>
+        <v>30.29780192</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1752027208731858</v>
+        <v>0.1771854485353813</v>
       </c>
       <c r="T44">
-        <v>1.550211252154449</v>
+        <v>1.573963818647278</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>63.8247020608589</v>
+        <v>62.34040666409474</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1182989056651673</v>
+        <v>0.1180794332238869</v>
       </c>
       <c r="C45">
-        <v>14.38992056346123</v>
+        <v>14.15735526995516</v>
       </c>
       <c r="D45">
-        <v>24.81292056346123</v>
+        <v>24.82435526995516</v>
       </c>
       <c r="E45">
-        <v>10.492</v>
+        <v>10.736</v>
       </c>
       <c r="F45">
-        <v>10.492</v>
+        <v>10.736</v>
       </c>
       <c r="G45">
         <v>0.06900000000000001</v>
@@ -4965,28 +4965,28 @@
         <v>32.9</v>
       </c>
       <c r="M45">
-        <v>0.5277476</v>
+        <v>0.5400208</v>
       </c>
       <c r="N45">
-        <v>32.3722524</v>
+        <v>32.3599792</v>
       </c>
       <c r="O45">
-        <v>6.474450480000001</v>
+        <v>6.47199584</v>
       </c>
       <c r="P45">
-        <v>25.89780192</v>
+        <v>25.88798336</v>
       </c>
       <c r="Q45">
-        <v>30.29780192</v>
+        <v>30.28798336</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1771854485353813</v>
+        <v>0.179238987899798</v>
       </c>
       <c r="T45">
-        <v>1.573963818647278</v>
+        <v>1.598564691086278</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>62.34040666409474</v>
+        <v>60.92357923991076</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1180794332238869</v>
+        <v>0.1178599607826064</v>
       </c>
       <c r="C46">
-        <v>14.15735526995516</v>
+        <v>13.92480052037483</v>
       </c>
       <c r="D46">
-        <v>24.82435526995516</v>
+        <v>24.83580052037483</v>
       </c>
       <c r="E46">
-        <v>10.736</v>
+        <v>10.98</v>
       </c>
       <c r="F46">
-        <v>10.736</v>
+        <v>10.98</v>
       </c>
       <c r="G46">
         <v>0.06900000000000001</v>
@@ -5047,28 +5047,28 @@
         <v>32.9</v>
       </c>
       <c r="M46">
-        <v>0.5400208</v>
+        <v>0.552294</v>
       </c>
       <c r="N46">
-        <v>32.3599792</v>
+        <v>32.347706</v>
       </c>
       <c r="O46">
-        <v>6.47199584</v>
+        <v>6.469541199999999</v>
       </c>
       <c r="P46">
-        <v>25.88798336</v>
+        <v>25.8781648</v>
       </c>
       <c r="Q46">
-        <v>30.28798336</v>
+        <v>30.2781648</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.179238987899798</v>
+        <v>0.1813672014229208</v>
       </c>
       <c r="T46">
-        <v>1.598564691086278</v>
+        <v>1.624060140704879</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>60.92357923991076</v>
+        <v>59.56972192346829</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1178599607826064</v>
+        <v>0.117640488341326</v>
       </c>
       <c r="C47">
-        <v>13.92480052037483</v>
+        <v>13.69225632931077</v>
       </c>
       <c r="D47">
-        <v>24.83580052037483</v>
+        <v>24.84725632931077</v>
       </c>
       <c r="E47">
-        <v>10.98</v>
+        <v>11.224</v>
       </c>
       <c r="F47">
-        <v>10.98</v>
+        <v>11.224</v>
       </c>
       <c r="G47">
         <v>0.06900000000000001</v>
@@ -5129,28 +5129,28 @@
         <v>32.9</v>
       </c>
       <c r="M47">
-        <v>0.552294</v>
+        <v>0.5645671999999999</v>
       </c>
       <c r="N47">
-        <v>32.347706</v>
+        <v>32.3354328</v>
       </c>
       <c r="O47">
-        <v>6.469541199999999</v>
+        <v>6.46708656</v>
       </c>
       <c r="P47">
-        <v>25.8781648</v>
+        <v>25.86834624</v>
       </c>
       <c r="Q47">
-        <v>30.2781648</v>
+        <v>30.26834624</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1813672014229208</v>
+        <v>0.1835742376691222</v>
       </c>
       <c r="T47">
-        <v>1.624060140704879</v>
+        <v>1.65049986623528</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>59.56972192346829</v>
+        <v>58.2747279686103</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.117640488341326</v>
+        <v>0.1174210159000455</v>
       </c>
       <c r="C48">
-        <v>13.69225632931077</v>
+        <v>13.45972271138046</v>
       </c>
       <c r="D48">
-        <v>24.84725632931077</v>
+        <v>24.85872271138046</v>
       </c>
       <c r="E48">
-        <v>11.224</v>
+        <v>11.468</v>
       </c>
       <c r="F48">
-        <v>11.224</v>
+        <v>11.468</v>
       </c>
       <c r="G48">
         <v>0.06900000000000001</v>
@@ -5211,28 +5211,28 @@
         <v>32.9</v>
       </c>
       <c r="M48">
-        <v>0.5645671999999999</v>
+        <v>0.5768403999999999</v>
       </c>
       <c r="N48">
-        <v>32.3354328</v>
+        <v>32.3231596</v>
       </c>
       <c r="O48">
-        <v>6.46708656</v>
+        <v>6.46463192</v>
       </c>
       <c r="P48">
-        <v>25.86834624</v>
+        <v>25.85852768</v>
       </c>
       <c r="Q48">
-        <v>30.26834624</v>
+        <v>30.25852768</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1835742376691222</v>
+        <v>0.1858645583019727</v>
       </c>
       <c r="T48">
-        <v>1.65049986623528</v>
+        <v>1.677937317257394</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>58.2747279686103</v>
+        <v>57.03484013949092</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1174210159000455</v>
+        <v>0.1172015434587651</v>
       </c>
       <c r="C49">
-        <v>13.45972271138046</v>
+        <v>13.22719968122836</v>
       </c>
       <c r="D49">
-        <v>24.85872271138046</v>
+        <v>24.87019968122836</v>
       </c>
       <c r="E49">
-        <v>11.468</v>
+        <v>11.712</v>
       </c>
       <c r="F49">
-        <v>11.468</v>
+        <v>11.712</v>
       </c>
       <c r="G49">
         <v>0.06900000000000001</v>
@@ -5293,28 +5293,28 @@
         <v>32.9</v>
       </c>
       <c r="M49">
-        <v>0.5768403999999999</v>
+        <v>0.5891135999999999</v>
       </c>
       <c r="N49">
-        <v>32.3231596</v>
+        <v>32.3108864</v>
       </c>
       <c r="O49">
-        <v>6.46463192</v>
+        <v>6.462177280000001</v>
       </c>
       <c r="P49">
-        <v>25.85852768</v>
+        <v>25.84870912</v>
       </c>
       <c r="Q49">
-        <v>30.25852768</v>
+        <v>30.24870912</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1858645583019727</v>
+        <v>0.1882429681899328</v>
       </c>
       <c r="T49">
-        <v>1.677937317257394</v>
+        <v>1.706430054857282</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>57.03484013949092</v>
+        <v>55.84661430325154</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1172015434587651</v>
+        <v>0.1169820710174846</v>
       </c>
       <c r="C50">
-        <v>13.22719968122836</v>
+        <v>12.99468725352598</v>
       </c>
       <c r="D50">
-        <v>24.87019968122836</v>
+        <v>24.88168725352598</v>
       </c>
       <c r="E50">
-        <v>11.712</v>
+        <v>11.956</v>
       </c>
       <c r="F50">
-        <v>11.712</v>
+        <v>11.956</v>
       </c>
       <c r="G50">
         <v>0.06900000000000001</v>
@@ -5375,28 +5375,28 @@
         <v>32.9</v>
       </c>
       <c r="M50">
-        <v>0.5891135999999999</v>
+        <v>0.6013868</v>
       </c>
       <c r="N50">
-        <v>32.3108864</v>
+        <v>32.2986132</v>
       </c>
       <c r="O50">
-        <v>6.462177280000001</v>
+        <v>6.45972264</v>
       </c>
       <c r="P50">
-        <v>25.84870912</v>
+        <v>25.83889056</v>
       </c>
       <c r="Q50">
-        <v>30.24870912</v>
+        <v>30.23889056</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1882429681899328</v>
+        <v>0.1907146490538914</v>
       </c>
       <c r="T50">
-        <v>1.706430054857282</v>
+        <v>1.736040154715989</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>55.84661430325154</v>
+        <v>54.70688748073619</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1169820710174846</v>
+        <v>0.1167625985762042</v>
       </c>
       <c r="C51">
-        <v>12.99468725352598</v>
+        <v>12.76218544297197</v>
       </c>
       <c r="D51">
-        <v>24.88168725352598</v>
+        <v>24.89318544297197</v>
       </c>
       <c r="E51">
-        <v>11.956</v>
+        <v>12.2</v>
       </c>
       <c r="F51">
-        <v>11.956</v>
+        <v>12.2</v>
       </c>
       <c r="G51">
         <v>0.06900000000000001</v>
@@ -5457,28 +5457,28 @@
         <v>32.9</v>
       </c>
       <c r="M51">
-        <v>0.6013868</v>
+        <v>0.61366</v>
       </c>
       <c r="N51">
-        <v>32.2986132</v>
+        <v>32.28634</v>
       </c>
       <c r="O51">
-        <v>6.45972264</v>
+        <v>6.457267999999999</v>
       </c>
       <c r="P51">
-        <v>25.83889056</v>
+        <v>25.829072</v>
       </c>
       <c r="Q51">
-        <v>30.23889056</v>
+        <v>30.229072</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1907146490538914</v>
+        <v>0.1932851971524083</v>
       </c>
       <c r="T51">
-        <v>1.736040154715989</v>
+        <v>1.766834658569044</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>54.70688748073619</v>
+        <v>53.61274973112146</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1167625985762042</v>
+        <v>0.1165431261349237</v>
       </c>
       <c r="C52">
-        <v>12.76218544297197</v>
+        <v>12.52969426429214</v>
       </c>
       <c r="D52">
-        <v>24.89318544297197</v>
+        <v>24.90469426429214</v>
       </c>
       <c r="E52">
-        <v>12.2</v>
+        <v>12.444</v>
       </c>
       <c r="F52">
-        <v>12.2</v>
+        <v>12.444</v>
       </c>
       <c r="G52">
         <v>0.06900000000000001</v>
@@ -5539,28 +5539,28 @@
         <v>32.9</v>
       </c>
       <c r="M52">
-        <v>0.61366</v>
+        <v>0.6259332</v>
       </c>
       <c r="N52">
-        <v>32.28634</v>
+        <v>32.2740668</v>
       </c>
       <c r="O52">
-        <v>6.457267999999999</v>
+        <v>6.45481336</v>
       </c>
       <c r="P52">
-        <v>25.829072</v>
+        <v>25.81925344</v>
       </c>
       <c r="Q52">
-        <v>30.229072</v>
+        <v>30.21925344</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1932851971524083</v>
+        <v>0.195960665581477</v>
       </c>
       <c r="T52">
-        <v>1.766834658569044</v>
+        <v>1.798886080946714</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>53.61274973112146</v>
+        <v>52.56151934423674</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1165431261349237</v>
+        <v>0.1163236536936433</v>
       </c>
       <c r="C53">
-        <v>12.52969426429214</v>
+        <v>12.29721373223956</v>
       </c>
       <c r="D53">
-        <v>24.90469426429214</v>
+        <v>24.91621373223956</v>
       </c>
       <c r="E53">
-        <v>12.444</v>
+        <v>12.688</v>
       </c>
       <c r="F53">
-        <v>12.444</v>
+        <v>12.688</v>
       </c>
       <c r="G53">
         <v>0.06900000000000001</v>
@@ -5621,28 +5621,28 @@
         <v>32.9</v>
       </c>
       <c r="M53">
-        <v>0.6259332</v>
+        <v>0.6382064</v>
       </c>
       <c r="N53">
-        <v>32.2740668</v>
+        <v>32.2617936</v>
       </c>
       <c r="O53">
-        <v>6.45481336</v>
+        <v>6.452358719999999</v>
       </c>
       <c r="P53">
-        <v>25.81925344</v>
+        <v>25.80943488</v>
       </c>
       <c r="Q53">
-        <v>30.21925344</v>
+        <v>30.20943488</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.195960665581477</v>
+        <v>0.1987476118617568</v>
       </c>
       <c r="T53">
-        <v>1.798886080946714</v>
+        <v>1.832272979256787</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>52.56151934423674</v>
+        <v>51.55072089530911</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1163236536936433</v>
+        <v>0.1161041812523628</v>
       </c>
       <c r="C54">
-        <v>12.29721373223956</v>
+        <v>12.0647438615946</v>
       </c>
       <c r="D54">
-        <v>24.91621373223956</v>
+        <v>24.9277438615946</v>
       </c>
       <c r="E54">
-        <v>12.688</v>
+        <v>12.932</v>
       </c>
       <c r="F54">
-        <v>12.688</v>
+        <v>12.932</v>
       </c>
       <c r="G54">
         <v>0.06900000000000001</v>
@@ -5703,28 +5703,28 @@
         <v>32.9</v>
       </c>
       <c r="M54">
-        <v>0.6382064</v>
+        <v>0.6504795999999999</v>
       </c>
       <c r="N54">
-        <v>32.2617936</v>
+        <v>32.2495204</v>
       </c>
       <c r="O54">
-        <v>6.452358719999999</v>
+        <v>6.44990408</v>
       </c>
       <c r="P54">
-        <v>25.80943488</v>
+        <v>25.79961632</v>
       </c>
       <c r="Q54">
-        <v>30.20943488</v>
+        <v>30.19961632</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1987476118617568</v>
+        <v>0.2016531516007719</v>
       </c>
       <c r="T54">
-        <v>1.832272979256787</v>
+        <v>1.867080596643884</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>51.55072089530911</v>
+        <v>50.57806578407686</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1161041812523628</v>
+        <v>0.1158847088110823</v>
       </c>
       <c r="C55">
-        <v>12.0647438615946</v>
+        <v>11.83228466716502</v>
       </c>
       <c r="D55">
-        <v>24.9277438615946</v>
+        <v>24.93928466716502</v>
       </c>
       <c r="E55">
-        <v>12.932</v>
+        <v>13.176</v>
       </c>
       <c r="F55">
-        <v>12.932</v>
+        <v>13.176</v>
       </c>
       <c r="G55">
         <v>0.06900000000000001</v>
@@ -5785,28 +5785,28 @@
         <v>32.9</v>
       </c>
       <c r="M55">
-        <v>0.6504795999999999</v>
+        <v>0.6627527999999999</v>
       </c>
       <c r="N55">
-        <v>32.2495204</v>
+        <v>32.2372472</v>
       </c>
       <c r="O55">
-        <v>6.44990408</v>
+        <v>6.44744944</v>
       </c>
       <c r="P55">
-        <v>25.79961632</v>
+        <v>25.78979776</v>
       </c>
       <c r="Q55">
-        <v>30.19961632</v>
+        <v>30.18979776</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2016531516007719</v>
+        <v>0.2046850191545269</v>
       </c>
       <c r="T55">
-        <v>1.867080596643884</v>
+        <v>1.903401588699985</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>50.57806578407686</v>
+        <v>49.64143493622358</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1158847088110823</v>
+        <v>0.1156652363698019</v>
       </c>
       <c r="C56">
-        <v>11.83228466716502</v>
+        <v>11.59983616378599</v>
       </c>
       <c r="D56">
-        <v>24.93928466716502</v>
+        <v>24.95083616378599</v>
       </c>
       <c r="E56">
-        <v>13.176</v>
+        <v>13.42</v>
       </c>
       <c r="F56">
-        <v>13.176</v>
+        <v>13.42</v>
       </c>
       <c r="G56">
         <v>0.06900000000000001</v>
@@ -5867,28 +5867,28 @@
         <v>32.9</v>
       </c>
       <c r="M56">
-        <v>0.6627527999999999</v>
+        <v>0.675026</v>
       </c>
       <c r="N56">
-        <v>32.2372472</v>
+        <v>32.224974</v>
       </c>
       <c r="O56">
-        <v>6.44744944</v>
+        <v>6.4449948</v>
       </c>
       <c r="P56">
-        <v>25.78979776</v>
+        <v>25.7799792</v>
       </c>
       <c r="Q56">
-        <v>30.18979776</v>
+        <v>30.17997919999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2046850191545269</v>
+        <v>0.2078516363773376</v>
       </c>
       <c r="T56">
-        <v>1.903401588699985</v>
+        <v>1.941336847069691</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>49.64143493622358</v>
+        <v>48.7388633919286</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1156652363698019</v>
+        <v>0.1154457639285214</v>
       </c>
       <c r="C57">
-        <v>11.59983616378599</v>
+        <v>11.36739836632019</v>
       </c>
       <c r="D57">
-        <v>24.95083616378599</v>
+        <v>24.96239836632019</v>
       </c>
       <c r="E57">
-        <v>13.42</v>
+        <v>13.664</v>
       </c>
       <c r="F57">
-        <v>13.42</v>
+        <v>13.664</v>
       </c>
       <c r="G57">
         <v>0.06900000000000001</v>
@@ -5949,28 +5949,28 @@
         <v>32.9</v>
       </c>
       <c r="M57">
-        <v>0.675026</v>
+        <v>0.6872992</v>
       </c>
       <c r="N57">
-        <v>32.224974</v>
+        <v>32.2127008</v>
       </c>
       <c r="O57">
-        <v>6.4449948</v>
+        <v>6.44254016</v>
       </c>
       <c r="P57">
-        <v>25.7799792</v>
+        <v>25.77016064</v>
       </c>
       <c r="Q57">
-        <v>30.17997919999999</v>
+        <v>30.17016064</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2078516363773376</v>
+        <v>0.2111621907466397</v>
       </c>
       <c r="T57">
-        <v>1.941336847069691</v>
+        <v>1.980996435365293</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>48.7388633919286</v>
+        <v>47.86852654564417</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1154457639285214</v>
+        <v>0.115226291487241</v>
       </c>
       <c r="C58">
-        <v>11.36739836632019</v>
+        <v>11.13497128965786</v>
       </c>
       <c r="D58">
-        <v>24.96239836632019</v>
+        <v>24.97397128965786</v>
       </c>
       <c r="E58">
-        <v>13.664</v>
+        <v>13.908</v>
       </c>
       <c r="F58">
-        <v>13.664</v>
+        <v>13.908</v>
       </c>
       <c r="G58">
         <v>0.06900000000000001</v>
@@ -6031,28 +6031,28 @@
         <v>32.9</v>
       </c>
       <c r="M58">
-        <v>0.6872992</v>
+        <v>0.6995724</v>
       </c>
       <c r="N58">
-        <v>32.2127008</v>
+        <v>32.2004276</v>
       </c>
       <c r="O58">
-        <v>6.44254016</v>
+        <v>6.44008552</v>
       </c>
       <c r="P58">
-        <v>25.77016064</v>
+        <v>25.76034208</v>
       </c>
       <c r="Q58">
-        <v>30.17016064</v>
+        <v>30.16034208</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2111621907466397</v>
+        <v>0.2146267243889326</v>
       </c>
       <c r="T58">
-        <v>1.980996435365293</v>
+        <v>2.022500655674643</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>47.86852654564417</v>
+        <v>47.02872783431707</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.115226291487241</v>
+        <v>0.1150068190459605</v>
       </c>
       <c r="C59">
-        <v>11.13497128965786</v>
+        <v>10.90255494871687</v>
       </c>
       <c r="D59">
-        <v>24.97397128965786</v>
+        <v>24.98555494871687</v>
       </c>
       <c r="E59">
-        <v>13.908</v>
+        <v>14.152</v>
       </c>
       <c r="F59">
-        <v>13.908</v>
+        <v>14.152</v>
       </c>
       <c r="G59">
         <v>0.06900000000000001</v>
@@ -6113,28 +6113,28 @@
         <v>32.9</v>
       </c>
       <c r="M59">
-        <v>0.6995724</v>
+        <v>0.7118456</v>
       </c>
       <c r="N59">
-        <v>32.2004276</v>
+        <v>32.1881544</v>
       </c>
       <c r="O59">
-        <v>6.44008552</v>
+        <v>6.43763088</v>
       </c>
       <c r="P59">
-        <v>25.76034208</v>
+        <v>25.75052352</v>
       </c>
       <c r="Q59">
-        <v>30.16034208</v>
+        <v>30.15052352</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2146267243889326</v>
+        <v>0.2182562358237156</v>
       </c>
       <c r="T59">
-        <v>2.022500655674643</v>
+        <v>2.065981267427296</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>47.02872783431707</v>
+        <v>46.21788769924265</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1150068190459605</v>
+        <v>0.1147873466046801</v>
       </c>
       <c r="C60">
-        <v>10.90255494871687</v>
+        <v>10.67014935844278</v>
       </c>
       <c r="D60">
-        <v>24.98555494871687</v>
+        <v>24.99714935844278</v>
       </c>
       <c r="E60">
-        <v>14.152</v>
+        <v>14.396</v>
       </c>
       <c r="F60">
-        <v>14.152</v>
+        <v>14.396</v>
       </c>
       <c r="G60">
         <v>0.06900000000000001</v>
@@ -6195,28 +6195,28 @@
         <v>32.9</v>
       </c>
       <c r="M60">
-        <v>0.7118455999999999</v>
+        <v>0.7241188</v>
       </c>
       <c r="N60">
-        <v>32.1881544</v>
+        <v>32.1758812</v>
       </c>
       <c r="O60">
-        <v>6.43763088</v>
+        <v>6.435176240000001</v>
       </c>
       <c r="P60">
-        <v>25.75052352</v>
+        <v>25.74070496</v>
       </c>
       <c r="Q60">
-        <v>30.15052352</v>
+        <v>30.14070496</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2182562358237155</v>
+        <v>0.2220627965967807</v>
       </c>
       <c r="T60">
-        <v>2.065981267427295</v>
+        <v>2.111582884631297</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>46.21788769924266</v>
+        <v>45.43453367044192</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1147873466046801</v>
+        <v>0.1145678741633996</v>
       </c>
       <c r="C61">
-        <v>10.67014935844278</v>
+        <v>10.4377545338089</v>
       </c>
       <c r="D61">
-        <v>24.99714935844278</v>
+        <v>25.0087545338089</v>
       </c>
       <c r="E61">
-        <v>14.396</v>
+        <v>14.64</v>
       </c>
       <c r="F61">
-        <v>14.396</v>
+        <v>14.64</v>
       </c>
       <c r="G61">
         <v>0.06900000000000001</v>
@@ -6277,28 +6277,28 @@
         <v>32.9</v>
       </c>
       <c r="M61">
-        <v>0.7241188</v>
+        <v>0.7363919999999999</v>
       </c>
       <c r="N61">
-        <v>32.1758812</v>
+        <v>32.163608</v>
       </c>
       <c r="O61">
-        <v>6.435176240000001</v>
+        <v>6.4327216</v>
       </c>
       <c r="P61">
-        <v>25.74070496</v>
+        <v>25.7308864</v>
       </c>
       <c r="Q61">
-        <v>30.14070496</v>
+        <v>30.13088639999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2220627965967807</v>
+        <v>0.2260596854084991</v>
       </c>
       <c r="T61">
-        <v>2.111582884631297</v>
+        <v>2.159464582695499</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>45.43453367044192</v>
+        <v>44.67729144260122</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1145678741633996</v>
+        <v>0.1143484017221192</v>
       </c>
       <c r="C62">
-        <v>10.4377545338089</v>
+        <v>10.20537048981636</v>
       </c>
       <c r="D62">
-        <v>25.0087545338089</v>
+        <v>25.02037048981636</v>
       </c>
       <c r="E62">
-        <v>14.64</v>
+        <v>14.884</v>
       </c>
       <c r="F62">
-        <v>14.64</v>
+        <v>14.884</v>
       </c>
       <c r="G62">
         <v>0.06900000000000001</v>
@@ -6359,28 +6359,28 @@
         <v>32.9</v>
       </c>
       <c r="M62">
-        <v>0.7363919999999999</v>
+        <v>0.7486651999999999</v>
       </c>
       <c r="N62">
-        <v>32.163608</v>
+        <v>32.1513348</v>
       </c>
       <c r="O62">
-        <v>6.4327216</v>
+        <v>6.430266960000001</v>
       </c>
       <c r="P62">
-        <v>25.7308864</v>
+        <v>25.72106784</v>
       </c>
       <c r="Q62">
-        <v>30.13088639999999</v>
+        <v>30.12106784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2260596854084991</v>
+        <v>0.2302615428772286</v>
       </c>
       <c r="T62">
-        <v>2.159464582695499</v>
+        <v>2.2098017524553</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>44.67729144260122</v>
+        <v>43.9448768287881</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1143484017221192</v>
+        <v>0.1141289292808387</v>
       </c>
       <c r="C63">
-        <v>10.20537048981636</v>
+        <v>9.972997241494175</v>
       </c>
       <c r="D63">
-        <v>25.02037048981636</v>
+        <v>25.03199724149417</v>
       </c>
       <c r="E63">
-        <v>14.884</v>
+        <v>15.128</v>
       </c>
       <c r="F63">
-        <v>14.884</v>
+        <v>15.128</v>
       </c>
       <c r="G63">
         <v>0.06900000000000001</v>
@@ -6441,28 +6441,28 @@
         <v>32.9</v>
       </c>
       <c r="M63">
-        <v>0.7486651999999999</v>
+        <v>0.7609383999999999</v>
       </c>
       <c r="N63">
-        <v>32.1513348</v>
+        <v>32.1390616</v>
       </c>
       <c r="O63">
-        <v>6.430266960000001</v>
+        <v>6.42781232</v>
       </c>
       <c r="P63">
-        <v>25.72106784</v>
+        <v>25.71124928</v>
       </c>
       <c r="Q63">
-        <v>30.12106784</v>
+        <v>30.11124928</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2302615428772286</v>
+        <v>0.2346845507390493</v>
       </c>
       <c r="T63">
-        <v>2.2098017524553</v>
+        <v>2.262788246939303</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>43.9448768287881</v>
+        <v>43.2360884928399</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1141289292808387</v>
+        <v>0.1139094568395582</v>
       </c>
       <c r="C64">
-        <v>9.972997241494175</v>
+        <v>9.740634803899308</v>
       </c>
       <c r="D64">
-        <v>25.03199724149417</v>
+        <v>25.04363480389931</v>
       </c>
       <c r="E64">
-        <v>15.128</v>
+        <v>15.372</v>
       </c>
       <c r="F64">
-        <v>15.128</v>
+        <v>15.372</v>
       </c>
       <c r="G64">
         <v>0.06900000000000001</v>
@@ -6523,28 +6523,28 @@
         <v>32.9</v>
       </c>
       <c r="M64">
-        <v>0.7609383999999999</v>
+        <v>0.7732116</v>
       </c>
       <c r="N64">
-        <v>32.1390616</v>
+        <v>32.1267884</v>
       </c>
       <c r="O64">
-        <v>6.42781232</v>
+        <v>6.425357679999999</v>
       </c>
       <c r="P64">
-        <v>25.71124928</v>
+        <v>25.70143072</v>
       </c>
       <c r="Q64">
-        <v>30.11124928</v>
+        <v>30.10143072</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2346845507390493</v>
+        <v>0.2393466401069142</v>
       </c>
       <c r="T64">
-        <v>2.262788246939303</v>
+        <v>2.318638876260278</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>43.2360884928399</v>
+        <v>42.54980137390592</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1139094568395582</v>
+        <v>0.1136899843982778</v>
       </c>
       <c r="C65">
-        <v>9.740634803899308</v>
+        <v>9.508283192116743</v>
       </c>
       <c r="D65">
-        <v>25.04363480389931</v>
+        <v>25.05528319211674</v>
       </c>
       <c r="E65">
-        <v>15.372</v>
+        <v>15.616</v>
       </c>
       <c r="F65">
-        <v>15.372</v>
+        <v>15.616</v>
       </c>
       <c r="G65">
         <v>0.06900000000000001</v>
@@ -6605,28 +6605,28 @@
         <v>32.9</v>
       </c>
       <c r="M65">
-        <v>0.7732116</v>
+        <v>0.7854848</v>
       </c>
       <c r="N65">
-        <v>32.1267884</v>
+        <v>32.1145152</v>
       </c>
       <c r="O65">
-        <v>6.425357679999999</v>
+        <v>6.42290304</v>
       </c>
       <c r="P65">
-        <v>25.70143072</v>
+        <v>25.69161216</v>
       </c>
       <c r="Q65">
-        <v>30.10143072</v>
+        <v>30.09161216</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2393466401069142</v>
+        <v>0.2442677344396606</v>
       </c>
       <c r="T65">
-        <v>2.318638876260278</v>
+        <v>2.377592318321307</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>42.54980137390592</v>
+        <v>41.88496072743865</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1136899843982778</v>
+        <v>0.1134705119569973</v>
       </c>
       <c r="C66">
-        <v>9.508283192116743</v>
+        <v>9.275942421259526</v>
       </c>
       <c r="D66">
-        <v>25.05528319211674</v>
+        <v>25.06694242125953</v>
       </c>
       <c r="E66">
-        <v>15.616</v>
+        <v>15.86</v>
       </c>
       <c r="F66">
-        <v>15.616</v>
+        <v>15.86</v>
       </c>
       <c r="G66">
         <v>0.06900000000000001</v>
@@ -6687,28 +6687,28 @@
         <v>32.9</v>
       </c>
       <c r="M66">
-        <v>0.7854848</v>
+        <v>0.797758</v>
       </c>
       <c r="N66">
-        <v>32.1145152</v>
+        <v>32.102242</v>
       </c>
       <c r="O66">
-        <v>6.42290304</v>
+        <v>6.4204484</v>
       </c>
       <c r="P66">
-        <v>25.69161216</v>
+        <v>25.6817936</v>
       </c>
       <c r="Q66">
-        <v>30.09161216</v>
+        <v>30.0817936</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2442677344396606</v>
+        <v>0.2494700341628496</v>
       </c>
       <c r="T66">
-        <v>2.377592318321307</v>
+        <v>2.439914528500109</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>41.88496072743865</v>
+        <v>41.24057671624728</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1134705119569973</v>
+        <v>0.1132510395157169</v>
       </c>
       <c r="C67">
-        <v>9.275942421259526</v>
+        <v>9.043612506468861</v>
       </c>
       <c r="D67">
-        <v>25.06694242125953</v>
+        <v>25.07861250646886</v>
       </c>
       <c r="E67">
-        <v>15.86</v>
+        <v>16.104</v>
       </c>
       <c r="F67">
-        <v>15.86</v>
+        <v>16.104</v>
       </c>
       <c r="G67">
         <v>0.06900000000000001</v>
@@ -6769,28 +6769,28 @@
         <v>32.9</v>
       </c>
       <c r="M67">
-        <v>0.797758</v>
+        <v>0.8100312</v>
       </c>
       <c r="N67">
-        <v>32.102242</v>
+        <v>32.0899688</v>
       </c>
       <c r="O67">
-        <v>6.4204484</v>
+        <v>6.417993760000001</v>
       </c>
       <c r="P67">
-        <v>25.6817936</v>
+        <v>25.67197504</v>
       </c>
       <c r="Q67">
-        <v>30.0817936</v>
+        <v>30.07197504</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2494700341628496</v>
+        <v>0.2549783515168144</v>
       </c>
       <c r="T67">
-        <v>2.439914528500109</v>
+        <v>2.50590275104237</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>41.24057671624728</v>
+        <v>40.61571949327384</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1132510395157169</v>
+        <v>0.1130315670744365</v>
       </c>
       <c r="C68">
-        <v>9.043612506468861</v>
+        <v>8.811293462914154</v>
       </c>
       <c r="D68">
-        <v>25.07861250646886</v>
+        <v>25.09029346291415</v>
       </c>
       <c r="E68">
-        <v>16.104</v>
+        <v>16.348</v>
       </c>
       <c r="F68">
-        <v>16.104</v>
+        <v>16.348</v>
       </c>
       <c r="G68">
         <v>0.06900000000000001</v>
@@ -6851,28 +6851,28 @@
         <v>32.9</v>
       </c>
       <c r="M68">
-        <v>0.8100312</v>
+        <v>0.8223043999999999</v>
       </c>
       <c r="N68">
-        <v>32.0899688</v>
+        <v>32.0776956</v>
       </c>
       <c r="O68">
-        <v>6.417993760000001</v>
+        <v>6.41553912</v>
       </c>
       <c r="P68">
-        <v>25.67197504</v>
+        <v>25.66215648</v>
       </c>
       <c r="Q68">
-        <v>30.07197504</v>
+        <v>30.06215648</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2549783515168144</v>
+        <v>0.2608205062861711</v>
       </c>
       <c r="T68">
-        <v>2.50590275104237</v>
+        <v>2.575890259799315</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>40.61571949327384</v>
+        <v>40.00951472471751</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1130315670744365</v>
+        <v>0.112812094633156</v>
       </c>
       <c r="C69">
-        <v>8.811293462914154</v>
+        <v>8.578985305793093</v>
       </c>
       <c r="D69">
-        <v>25.09029346291415</v>
+        <v>25.10198530579309</v>
       </c>
       <c r="E69">
-        <v>16.348</v>
+        <v>16.592</v>
       </c>
       <c r="F69">
-        <v>16.348</v>
+        <v>16.592</v>
       </c>
       <c r="G69">
         <v>0.06900000000000001</v>
@@ -6933,28 +6933,28 @@
         <v>32.9</v>
       </c>
       <c r="M69">
-        <v>0.8223043999999999</v>
+        <v>0.8345775999999999</v>
       </c>
       <c r="N69">
-        <v>32.0776956</v>
+        <v>32.0654224</v>
       </c>
       <c r="O69">
-        <v>6.41553912</v>
+        <v>6.413084479999999</v>
       </c>
       <c r="P69">
-        <v>25.66215648</v>
+        <v>25.65233792</v>
       </c>
       <c r="Q69">
-        <v>30.06215648</v>
+        <v>30.05233792</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2608205062861711</v>
+        <v>0.2670277957286125</v>
       </c>
       <c r="T69">
-        <v>2.575890259799315</v>
+        <v>2.650251987853567</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>40.00951472471751</v>
+        <v>39.42113950817755</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.112812094633156</v>
+        <v>0.1125926221918755</v>
       </c>
       <c r="C70">
-        <v>8.578985305793093</v>
+        <v>8.346688050331689</v>
       </c>
       <c r="D70">
-        <v>25.10198530579309</v>
+        <v>25.11368805033169</v>
       </c>
       <c r="E70">
-        <v>16.592</v>
+        <v>16.836</v>
       </c>
       <c r="F70">
-        <v>16.592</v>
+        <v>16.836</v>
       </c>
       <c r="G70">
         <v>0.06900000000000001</v>
@@ -7015,28 +7015,28 @@
         <v>32.9</v>
       </c>
       <c r="M70">
-        <v>0.8345775999999999</v>
+        <v>0.8468508</v>
       </c>
       <c r="N70">
-        <v>32.0654224</v>
+        <v>32.0531492</v>
       </c>
       <c r="O70">
-        <v>6.413084479999999</v>
+        <v>6.41062984</v>
       </c>
       <c r="P70">
-        <v>25.65233792</v>
+        <v>25.64251936</v>
       </c>
       <c r="Q70">
-        <v>30.05233792</v>
+        <v>30.04251936</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2670277957286125</v>
+        <v>0.2736355554576631</v>
       </c>
       <c r="T70">
-        <v>2.650251987853567</v>
+        <v>2.72941124675003</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>39.42113950817755</v>
+        <v>38.84981864574019</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1125926221918755</v>
+        <v>0.1123731497505951</v>
       </c>
       <c r="C71">
-        <v>8.346688050331689</v>
+        <v>8.114401711784399</v>
       </c>
       <c r="D71">
-        <v>25.11368805033169</v>
+        <v>25.1254017117844</v>
       </c>
       <c r="E71">
-        <v>16.836</v>
+        <v>17.08</v>
       </c>
       <c r="F71">
-        <v>16.836</v>
+        <v>17.08</v>
       </c>
       <c r="G71">
         <v>0.06900000000000001</v>
@@ -7097,28 +7097,28 @@
         <v>32.9</v>
       </c>
       <c r="M71">
-        <v>0.8468508</v>
+        <v>0.859124</v>
       </c>
       <c r="N71">
-        <v>32.0531492</v>
+        <v>32.040876</v>
       </c>
       <c r="O71">
-        <v>6.41062984</v>
+        <v>6.4081752</v>
       </c>
       <c r="P71">
-        <v>25.64251936</v>
+        <v>25.6327008</v>
       </c>
       <c r="Q71">
-        <v>30.04251936</v>
+        <v>30.0327008</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2736355554576631</v>
+        <v>0.2806838325019836</v>
       </c>
       <c r="T71">
-        <v>2.72941124675003</v>
+        <v>2.813847789572923</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>38.84981864574019</v>
+        <v>38.29482123651533</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1123731497505951</v>
+        <v>0.1121536773093146</v>
       </c>
       <c r="C72">
-        <v>8.114401711784399</v>
+        <v>7.88212630543411</v>
       </c>
       <c r="D72">
-        <v>25.1254017117844</v>
+        <v>25.13712630543411</v>
       </c>
       <c r="E72">
-        <v>17.08</v>
+        <v>17.324</v>
       </c>
       <c r="F72">
-        <v>17.08</v>
+        <v>17.324</v>
       </c>
       <c r="G72">
         <v>0.06900000000000001</v>
@@ -7179,28 +7179,28 @@
         <v>32.9</v>
       </c>
       <c r="M72">
-        <v>0.859124</v>
+        <v>0.8713972</v>
       </c>
       <c r="N72">
-        <v>32.040876</v>
+        <v>32.0286028</v>
       </c>
       <c r="O72">
-        <v>6.4081752</v>
+        <v>6.405720560000001</v>
       </c>
       <c r="P72">
-        <v>25.6327008</v>
+        <v>25.62288224</v>
       </c>
       <c r="Q72">
-        <v>30.0327008</v>
+        <v>30.02288224</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2806838325019836</v>
+        <v>0.2882181976183264</v>
       </c>
       <c r="T72">
-        <v>2.813847789572923</v>
+        <v>2.904107542245672</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>38.29482123651533</v>
+        <v>37.7554575571278</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1121536773093146</v>
+        <v>0.1119342048680342</v>
       </c>
       <c r="C73">
-        <v>7.882126305434113</v>
+        <v>7.649861846592273</v>
       </c>
       <c r="D73">
-        <v>25.13712630543411</v>
+        <v>25.14886184659227</v>
       </c>
       <c r="E73">
-        <v>17.324</v>
+        <v>17.568</v>
       </c>
       <c r="F73">
-        <v>17.324</v>
+        <v>17.568</v>
       </c>
       <c r="G73">
         <v>0.06900000000000001</v>
@@ -7261,28 +7261,28 @@
         <v>32.9</v>
       </c>
       <c r="M73">
-        <v>0.8713971999999999</v>
+        <v>0.8836703999999999</v>
       </c>
       <c r="N73">
-        <v>32.0286028</v>
+        <v>32.0163296</v>
       </c>
       <c r="O73">
-        <v>6.405720560000001</v>
+        <v>6.40326592</v>
       </c>
       <c r="P73">
-        <v>25.62288224</v>
+        <v>25.61306368</v>
       </c>
       <c r="Q73">
-        <v>30.02288224</v>
+        <v>30.01306368</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2882181976183263</v>
+        <v>0.2962907316715506</v>
       </c>
       <c r="T73">
-        <v>2.904107542245671</v>
+        <v>3.000814420109329</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>37.75545755712781</v>
+        <v>37.23107620216769</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1119342048680342</v>
+        <v>0.1117147324267537</v>
       </c>
       <c r="C74">
-        <v>7.649861846592273</v>
+        <v>7.41760835059894</v>
       </c>
       <c r="D74">
-        <v>25.14886184659227</v>
+        <v>25.16060835059894</v>
       </c>
       <c r="E74">
-        <v>17.568</v>
+        <v>17.812</v>
       </c>
       <c r="F74">
-        <v>17.568</v>
+        <v>17.812</v>
       </c>
       <c r="G74">
         <v>0.06900000000000001</v>
@@ -7343,28 +7343,28 @@
         <v>32.9</v>
       </c>
       <c r="M74">
-        <v>0.8836703999999999</v>
+        <v>0.8959435999999998</v>
       </c>
       <c r="N74">
-        <v>32.0163296</v>
+        <v>32.0040564</v>
       </c>
       <c r="O74">
-        <v>6.40326592</v>
+        <v>6.400811279999999</v>
       </c>
       <c r="P74">
-        <v>25.61306368</v>
+        <v>25.60324512</v>
       </c>
       <c r="Q74">
-        <v>30.01306368</v>
+        <v>30.00324512</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2962907316715506</v>
+        <v>0.304961231210199</v>
       </c>
       <c r="T74">
-        <v>3.000814420109329</v>
+        <v>3.104684770407333</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>37.23107620216769</v>
+        <v>36.72106145967224</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1117147324267537</v>
+        <v>0.1114952599854733</v>
       </c>
       <c r="C75">
-        <v>7.41760835059894</v>
+        <v>7.185365832822839</v>
       </c>
       <c r="D75">
-        <v>25.16060835059894</v>
+        <v>25.17236583282284</v>
       </c>
       <c r="E75">
-        <v>17.812</v>
+        <v>18.056</v>
       </c>
       <c r="F75">
-        <v>17.812</v>
+        <v>18.056</v>
       </c>
       <c r="G75">
         <v>0.06900000000000001</v>
@@ -7425,28 +7425,28 @@
         <v>32.9</v>
       </c>
       <c r="M75">
-        <v>0.8959435999999998</v>
+        <v>0.9082167999999998</v>
       </c>
       <c r="N75">
-        <v>32.0040564</v>
+        <v>31.9917832</v>
       </c>
       <c r="O75">
-        <v>6.400811279999999</v>
+        <v>6.39835664</v>
       </c>
       <c r="P75">
-        <v>25.60324512</v>
+        <v>25.59342656</v>
       </c>
       <c r="Q75">
-        <v>30.00324512</v>
+        <v>29.99342656</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.304961231210199</v>
+        <v>0.3142986922518203</v>
       </c>
       <c r="T75">
-        <v>3.104684770407333</v>
+        <v>3.216545147651337</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>36.72106145967224</v>
+        <v>36.22483089940641</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1114952599854733</v>
+        <v>0.1112757875441928</v>
       </c>
       <c r="C76">
-        <v>7.185365832822839</v>
+        <v>6.953134308661429</v>
       </c>
       <c r="D76">
-        <v>25.17236583282284</v>
+        <v>25.18413430866143</v>
       </c>
       <c r="E76">
-        <v>18.056</v>
+        <v>18.3</v>
       </c>
       <c r="F76">
-        <v>18.056</v>
+        <v>18.3</v>
       </c>
       <c r="G76">
         <v>0.06900000000000001</v>
@@ -7507,28 +7507,28 @@
         <v>32.9</v>
       </c>
       <c r="M76">
-        <v>0.9082167999999998</v>
+        <v>0.9204899999999998</v>
       </c>
       <c r="N76">
-        <v>31.9917832</v>
+        <v>31.97951</v>
       </c>
       <c r="O76">
-        <v>6.39835664</v>
+        <v>6.395902</v>
       </c>
       <c r="P76">
-        <v>25.59342656</v>
+        <v>25.583608</v>
       </c>
       <c r="Q76">
-        <v>29.99342656</v>
+        <v>29.983608</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3142986922518203</v>
+        <v>0.3243831501767713</v>
       </c>
       <c r="T76">
-        <v>3.216545147651337</v>
+        <v>3.337354355074862</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>36.22483089940641</v>
+        <v>35.74183315408099</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1112757875441928</v>
+        <v>0.1110563151029124</v>
       </c>
       <c r="C77">
-        <v>6.953134308661429</v>
+        <v>6.720913793540987</v>
       </c>
       <c r="D77">
-        <v>25.18413430866143</v>
+        <v>25.19591379354099</v>
       </c>
       <c r="E77">
-        <v>18.3</v>
+        <v>18.544</v>
       </c>
       <c r="F77">
-        <v>18.3</v>
+        <v>18.544</v>
       </c>
       <c r="G77">
         <v>0.06900000000000001</v>
@@ -7589,28 +7589,28 @@
         <v>32.9</v>
       </c>
       <c r="M77">
-        <v>0.9204899999999998</v>
+        <v>0.9327632</v>
       </c>
       <c r="N77">
-        <v>31.97951</v>
+        <v>31.9672368</v>
       </c>
       <c r="O77">
-        <v>6.395902</v>
+        <v>6.39344736</v>
       </c>
       <c r="P77">
-        <v>25.583608</v>
+        <v>25.57378944</v>
       </c>
       <c r="Q77">
-        <v>29.983608</v>
+        <v>29.97378944</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3243831501767713</v>
+        <v>0.3353079795954682</v>
       </c>
       <c r="T77">
-        <v>3.337354355074862</v>
+        <v>3.468230996450347</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>35.74183315408099</v>
+        <v>35.27154587573781</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1110563151029124</v>
+        <v>0.1108368426616319</v>
       </c>
       <c r="C78">
-        <v>6.720913793540987</v>
+        <v>6.488704302916663</v>
       </c>
       <c r="D78">
-        <v>25.19591379354099</v>
+        <v>25.20770430291666</v>
       </c>
       <c r="E78">
-        <v>18.544</v>
+        <v>18.788</v>
       </c>
       <c r="F78">
-        <v>18.544</v>
+        <v>18.788</v>
       </c>
       <c r="G78">
         <v>0.06900000000000001</v>
@@ -7671,28 +7671,28 @@
         <v>32.9</v>
       </c>
       <c r="M78">
-        <v>0.9327632</v>
+        <v>0.9450364</v>
       </c>
       <c r="N78">
-        <v>31.9672368</v>
+        <v>31.9549636</v>
       </c>
       <c r="O78">
-        <v>6.39344736</v>
+        <v>6.39099272</v>
       </c>
       <c r="P78">
-        <v>25.57378944</v>
+        <v>25.56397088</v>
       </c>
       <c r="Q78">
-        <v>29.97378944</v>
+        <v>29.96397088</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3353079795954682</v>
+        <v>0.3471827941810084</v>
       </c>
       <c r="T78">
-        <v>3.468230996450347</v>
+        <v>3.610488215336744</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>35.27154587573781</v>
+        <v>34.81347385137757</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1108368426616319</v>
+        <v>0.1106173702203515</v>
       </c>
       <c r="C79">
-        <v>6.488704302916663</v>
+        <v>6.256505852272557</v>
       </c>
       <c r="D79">
-        <v>25.20770430291666</v>
+        <v>25.21950585227256</v>
       </c>
       <c r="E79">
-        <v>18.788</v>
+        <v>19.032</v>
       </c>
       <c r="F79">
-        <v>18.788</v>
+        <v>19.032</v>
       </c>
       <c r="G79">
         <v>0.06900000000000001</v>
@@ -7753,28 +7753,28 @@
         <v>32.9</v>
       </c>
       <c r="M79">
-        <v>0.9450364</v>
+        <v>0.9573096</v>
       </c>
       <c r="N79">
-        <v>31.9549636</v>
+        <v>31.9426904</v>
       </c>
       <c r="O79">
-        <v>6.39099272</v>
+        <v>6.38853808</v>
       </c>
       <c r="P79">
-        <v>25.56397088</v>
+        <v>25.55415232</v>
       </c>
       <c r="Q79">
-        <v>29.96397088</v>
+        <v>29.95415232</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3471827941810084</v>
+        <v>0.360137137365234</v>
       </c>
       <c r="T79">
-        <v>3.610488215336744</v>
+        <v>3.765677908667358</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>34.81347385137757</v>
+        <v>34.3671472635394</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1106173702203515</v>
+        <v>0.110397897779071</v>
       </c>
       <c r="C80">
-        <v>6.256505852272557</v>
+        <v>6.024318457121762</v>
       </c>
       <c r="D80">
-        <v>25.21950585227256</v>
+        <v>25.23131845712176</v>
       </c>
       <c r="E80">
-        <v>19.032</v>
+        <v>19.276</v>
       </c>
       <c r="F80">
-        <v>19.032</v>
+        <v>19.276</v>
       </c>
       <c r="G80">
         <v>0.06900000000000001</v>
@@ -7835,28 +7835,28 @@
         <v>32.9</v>
       </c>
       <c r="M80">
-        <v>0.9573096</v>
+        <v>0.9695828</v>
       </c>
       <c r="N80">
-        <v>31.9426904</v>
+        <v>31.9304172</v>
       </c>
       <c r="O80">
-        <v>6.38853808</v>
+        <v>6.38608344</v>
       </c>
       <c r="P80">
-        <v>25.55415232</v>
+        <v>25.54433376</v>
       </c>
       <c r="Q80">
-        <v>29.95415232</v>
+        <v>29.94433376</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.360137137365234</v>
+        <v>0.3743252275193858</v>
       </c>
       <c r="T80">
-        <v>3.765677908667358</v>
+        <v>3.935647572791364</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>34.3671472635394</v>
+        <v>33.93212008298827</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.110397897779071</v>
+        <v>0.1101784253377905</v>
       </c>
       <c r="C81">
-        <v>6.024318457121762</v>
+        <v>5.792142133006461</v>
       </c>
       <c r="D81">
-        <v>25.23131845712176</v>
+        <v>25.24314213300646</v>
       </c>
       <c r="E81">
-        <v>19.276</v>
+        <v>19.52</v>
       </c>
       <c r="F81">
-        <v>19.276</v>
+        <v>19.52</v>
       </c>
       <c r="G81">
         <v>0.06900000000000001</v>
@@ -7917,28 +7917,28 @@
         <v>32.9</v>
       </c>
       <c r="M81">
-        <v>0.9695828</v>
+        <v>0.981856</v>
       </c>
       <c r="N81">
-        <v>31.9304172</v>
+        <v>31.918144</v>
       </c>
       <c r="O81">
-        <v>6.38608344</v>
+        <v>6.3836288</v>
       </c>
       <c r="P81">
-        <v>25.54433376</v>
+        <v>25.5345152</v>
       </c>
       <c r="Q81">
-        <v>29.94433376</v>
+        <v>29.9345152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3743252275193858</v>
+        <v>0.3899321266889528</v>
       </c>
       <c r="T81">
-        <v>3.935647572791364</v>
+        <v>4.122614203327771</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>33.93212008298827</v>
+        <v>33.50796858195092</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1101784253377905</v>
+        <v>0.1099589528965101</v>
       </c>
       <c r="C82">
-        <v>5.792142133006461</v>
+        <v>5.559976895497972</v>
       </c>
       <c r="D82">
-        <v>25.24314213300646</v>
+        <v>25.25497689549797</v>
       </c>
       <c r="E82">
-        <v>19.52</v>
+        <v>19.764</v>
       </c>
       <c r="F82">
-        <v>19.52</v>
+        <v>19.764</v>
       </c>
       <c r="G82">
         <v>0.06900000000000001</v>
@@ -7999,28 +7999,28 @@
         <v>32.9</v>
       </c>
       <c r="M82">
-        <v>0.981856</v>
+        <v>0.9941291999999999</v>
       </c>
       <c r="N82">
-        <v>31.918144</v>
+        <v>31.9058708</v>
       </c>
       <c r="O82">
-        <v>6.3836288</v>
+        <v>6.38117416</v>
       </c>
       <c r="P82">
-        <v>25.5345152</v>
+        <v>25.52469664</v>
       </c>
       <c r="Q82">
-        <v>29.9345152</v>
+        <v>29.92469664</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3899321266889528</v>
+        <v>0.4071818573500533</v>
       </c>
       <c r="T82">
-        <v>4.122614203327771</v>
+        <v>4.32926153181538</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>33.50796858195092</v>
+        <v>33.09428995748239</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1099589528965101</v>
+        <v>0.1097394804552296</v>
       </c>
       <c r="C83">
-        <v>5.559976895497972</v>
+        <v>5.327822760196852</v>
       </c>
       <c r="D83">
-        <v>25.25497689549797</v>
+        <v>25.26682276019685</v>
       </c>
       <c r="E83">
-        <v>19.764</v>
+        <v>20.008</v>
       </c>
       <c r="F83">
-        <v>19.764</v>
+        <v>20.008</v>
       </c>
       <c r="G83">
         <v>0.06900000000000001</v>
@@ -8081,28 +8081,28 @@
         <v>32.9</v>
       </c>
       <c r="M83">
-        <v>0.9941291999999999</v>
+        <v>1.0064024</v>
       </c>
       <c r="N83">
-        <v>31.9058708</v>
+        <v>31.8935976</v>
       </c>
       <c r="O83">
-        <v>6.38117416</v>
+        <v>6.378719520000001</v>
       </c>
       <c r="P83">
-        <v>25.52469664</v>
+        <v>25.51487808</v>
       </c>
       <c r="Q83">
-        <v>29.92469664</v>
+        <v>29.91487808</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4071818573500533</v>
+        <v>0.4263482247512759</v>
       </c>
       <c r="T83">
-        <v>4.32926153181538</v>
+        <v>4.558869674579388</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>33.09428995748239</v>
+        <v>32.69070105556187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1097394804552296</v>
+        <v>0.1095200080139492</v>
       </c>
       <c r="C84">
-        <v>5.327822760196852</v>
+        <v>5.095679742732923</v>
       </c>
       <c r="D84">
-        <v>25.26682276019685</v>
+        <v>25.27867974273292</v>
       </c>
       <c r="E84">
-        <v>20.008</v>
+        <v>20.252</v>
       </c>
       <c r="F84">
-        <v>20.008</v>
+        <v>20.252</v>
       </c>
       <c r="G84">
         <v>0.06900000000000001</v>
@@ -8163,28 +8163,28 @@
         <v>32.9</v>
       </c>
       <c r="M84">
-        <v>1.0064024</v>
+        <v>1.0186756</v>
       </c>
       <c r="N84">
-        <v>31.8935976</v>
+        <v>31.8813244</v>
       </c>
       <c r="O84">
-        <v>6.378719520000001</v>
+        <v>6.37626488</v>
       </c>
       <c r="P84">
-        <v>25.51487808</v>
+        <v>25.50505952</v>
       </c>
       <c r="Q84">
-        <v>29.91487808</v>
+        <v>29.90505951999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4263482247512759</v>
+        <v>0.4477694589055836</v>
       </c>
       <c r="T84">
-        <v>4.558869674579388</v>
+        <v>4.815490540021515</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>32.69070105556187</v>
+        <v>32.29683718742257</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1095200080139492</v>
+        <v>0.1093005355726687</v>
       </c>
       <c r="C85">
-        <v>5.095679742732923</v>
+        <v>4.863547858765354</v>
       </c>
       <c r="D85">
-        <v>25.27867974273292</v>
+        <v>25.29054785876536</v>
       </c>
       <c r="E85">
-        <v>20.252</v>
+        <v>20.496</v>
       </c>
       <c r="F85">
-        <v>20.252</v>
+        <v>20.496</v>
       </c>
       <c r="G85">
         <v>0.06900000000000001</v>
@@ -8245,28 +8245,28 @@
         <v>32.9</v>
       </c>
       <c r="M85">
-        <v>1.0186756</v>
+        <v>1.0309488</v>
       </c>
       <c r="N85">
-        <v>31.8813244</v>
+        <v>31.8690512</v>
       </c>
       <c r="O85">
-        <v>6.37626488</v>
+        <v>6.37381024</v>
       </c>
       <c r="P85">
-        <v>25.50505952</v>
+        <v>25.49524096</v>
       </c>
       <c r="Q85">
-        <v>29.90505951999999</v>
+        <v>29.89524096</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4477694589055836</v>
+        <v>0.4718683473291798</v>
       </c>
       <c r="T85">
-        <v>4.815490540021515</v>
+        <v>5.104189013643909</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>32.29683718742257</v>
+        <v>31.91235103042944</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1093005355726687</v>
+        <v>0.1090810631313883</v>
       </c>
       <c r="C86">
-        <v>4.863547858765358</v>
+        <v>4.63142712398276</v>
       </c>
       <c r="D86">
-        <v>25.29054785876536</v>
+        <v>25.30242712398276</v>
       </c>
       <c r="E86">
-        <v>20.496</v>
+        <v>20.74</v>
       </c>
       <c r="F86">
-        <v>20.496</v>
+        <v>20.74</v>
       </c>
       <c r="G86">
         <v>0.06900000000000001</v>
@@ -8327,28 +8327,28 @@
         <v>32.9</v>
       </c>
       <c r="M86">
-        <v>1.0309488</v>
+        <v>1.043222</v>
       </c>
       <c r="N86">
-        <v>31.8690512</v>
+        <v>31.856778</v>
       </c>
       <c r="O86">
-        <v>6.37381024</v>
+        <v>6.3713556</v>
       </c>
       <c r="P86">
-        <v>25.49524096</v>
+        <v>25.4854224</v>
       </c>
       <c r="Q86">
-        <v>29.89524096</v>
+        <v>29.8854224</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4718683473291795</v>
+        <v>0.4991804208759218</v>
       </c>
       <c r="T86">
-        <v>5.104189013643905</v>
+        <v>5.431380617082618</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>31.91235103042945</v>
+        <v>31.53691160654204</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1090810631313883</v>
+        <v>0.1088615906901078</v>
       </c>
       <c r="C87">
-        <v>4.63142712398276</v>
+        <v>4.399317554103217</v>
       </c>
       <c r="D87">
-        <v>25.30242712398276</v>
+        <v>25.31431755410322</v>
       </c>
       <c r="E87">
-        <v>20.74</v>
+        <v>20.984</v>
       </c>
       <c r="F87">
-        <v>20.74</v>
+        <v>20.984</v>
       </c>
       <c r="G87">
         <v>0.06900000000000001</v>
@@ -8409,28 +8409,28 @@
         <v>32.9</v>
       </c>
       <c r="M87">
-        <v>1.043222</v>
+        <v>1.0554952</v>
       </c>
       <c r="N87">
-        <v>31.856778</v>
+        <v>31.8445048</v>
       </c>
       <c r="O87">
-        <v>6.3713556</v>
+        <v>6.36890096</v>
       </c>
       <c r="P87">
-        <v>25.4854224</v>
+        <v>25.47560384</v>
       </c>
       <c r="Q87">
-        <v>29.8854224</v>
+        <v>29.87560384</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4991804208759218</v>
+        <v>0.5303942192150559</v>
       </c>
       <c r="T87">
-        <v>5.431380617082618</v>
+        <v>5.805313878155432</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>31.53691160654204</v>
+        <v>31.17020333204736</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1088615906901078</v>
+        <v>0.1086421182488274</v>
       </c>
       <c r="C88">
-        <v>4.399317554103217</v>
+        <v>4.167219164874378</v>
       </c>
       <c r="D88">
-        <v>25.31431755410322</v>
+        <v>25.32621916487438</v>
       </c>
       <c r="E88">
-        <v>20.984</v>
+        <v>21.228</v>
       </c>
       <c r="F88">
-        <v>20.984</v>
+        <v>21.228</v>
       </c>
       <c r="G88">
         <v>0.06900000000000001</v>
@@ -8491,28 +8491,28 @@
         <v>32.9</v>
       </c>
       <c r="M88">
-        <v>1.0554952</v>
+        <v>1.0677684</v>
       </c>
       <c r="N88">
-        <v>31.8445048</v>
+        <v>31.8322316</v>
       </c>
       <c r="O88">
-        <v>6.36890096</v>
+        <v>6.366446320000001</v>
       </c>
       <c r="P88">
-        <v>25.47560384</v>
+        <v>25.46578528</v>
       </c>
       <c r="Q88">
-        <v>29.87560384</v>
+        <v>29.86578528</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5303942192150559</v>
+        <v>0.5664101403755951</v>
       </c>
       <c r="T88">
-        <v>5.805313878155432</v>
+        <v>6.236775333239447</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>31.17020333204736</v>
+        <v>30.81192513282843</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1086421182488274</v>
+        <v>0.1084226458075469</v>
       </c>
       <c r="C89">
-        <v>4.167219164874378</v>
+        <v>3.935131972073521</v>
       </c>
       <c r="D89">
-        <v>25.32621916487438</v>
+        <v>25.33813197207352</v>
       </c>
       <c r="E89">
-        <v>21.228</v>
+        <v>21.472</v>
       </c>
       <c r="F89">
-        <v>21.228</v>
+        <v>21.472</v>
       </c>
       <c r="G89">
         <v>0.06900000000000001</v>
@@ -8573,28 +8573,28 @@
         <v>32.9</v>
       </c>
       <c r="M89">
-        <v>1.0677684</v>
+        <v>1.0800416</v>
       </c>
       <c r="N89">
-        <v>31.8322316</v>
+        <v>31.8199584</v>
       </c>
       <c r="O89">
-        <v>6.366446320000001</v>
+        <v>6.36399168</v>
       </c>
       <c r="P89">
-        <v>25.46578528</v>
+        <v>25.45596672</v>
       </c>
       <c r="Q89">
-        <v>29.86578528</v>
+        <v>29.85596672</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5664101403755951</v>
+        <v>0.608428715062891</v>
       </c>
       <c r="T89">
-        <v>6.236775333239447</v>
+        <v>6.740147030837466</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>30.81192513282843</v>
+        <v>30.46178961995538</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1084226458075469</v>
+        <v>0.1082031733662665</v>
       </c>
       <c r="C90">
-        <v>3.935131972073521</v>
+        <v>3.703055991507622</v>
       </c>
       <c r="D90">
-        <v>25.33813197207352</v>
+        <v>25.35005599150762</v>
       </c>
       <c r="E90">
-        <v>21.472</v>
+        <v>21.716</v>
       </c>
       <c r="F90">
-        <v>21.472</v>
+        <v>21.716</v>
       </c>
       <c r="G90">
         <v>0.06900000000000001</v>
@@ -8655,28 +8655,28 @@
         <v>32.9</v>
       </c>
       <c r="M90">
-        <v>1.0800416</v>
+        <v>1.0923148</v>
       </c>
       <c r="N90">
-        <v>31.8199584</v>
+        <v>31.8076852</v>
       </c>
       <c r="O90">
-        <v>6.36399168</v>
+        <v>6.36153704</v>
       </c>
       <c r="P90">
-        <v>25.45596672</v>
+        <v>25.44614816</v>
       </c>
       <c r="Q90">
-        <v>29.85596672</v>
+        <v>29.84614816</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.608428715062891</v>
+        <v>0.6580870306024225</v>
       </c>
       <c r="T90">
-        <v>6.740147030837466</v>
+        <v>7.335040855271489</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>30.46178961995538</v>
+        <v>30.11952232085476</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1082031733662665</v>
+        <v>0.107983700924986</v>
       </c>
       <c r="C91">
-        <v>3.703055991507622</v>
+        <v>3.470991239013426</v>
       </c>
       <c r="D91">
-        <v>25.35005599150762</v>
+        <v>25.36199123901343</v>
       </c>
       <c r="E91">
-        <v>21.716</v>
+        <v>21.96</v>
       </c>
       <c r="F91">
-        <v>21.716</v>
+        <v>21.96</v>
       </c>
       <c r="G91">
         <v>0.06900000000000001</v>
@@ -8737,28 +8737,28 @@
         <v>32.9</v>
       </c>
       <c r="M91">
-        <v>1.0923148</v>
+        <v>1.104588</v>
       </c>
       <c r="N91">
-        <v>31.8076852</v>
+        <v>31.795412</v>
       </c>
       <c r="O91">
-        <v>6.36153704</v>
+        <v>6.3590824</v>
       </c>
       <c r="P91">
-        <v>25.44614816</v>
+        <v>25.4363296</v>
       </c>
       <c r="Q91">
-        <v>29.84614816</v>
+        <v>29.8363296</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6580870306024225</v>
+        <v>0.7176770092498602</v>
       </c>
       <c r="T91">
-        <v>7.335040855271489</v>
+        <v>8.048913444592316</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>30.11952232085476</v>
+        <v>29.78486096173415</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.107983700924986</v>
+        <v>0.1077642284837056</v>
       </c>
       <c r="C92">
-        <v>3.470991239013426</v>
+        <v>3.238937730457526</v>
       </c>
       <c r="D92">
-        <v>25.36199123901343</v>
+        <v>25.37393773045753</v>
       </c>
       <c r="E92">
-        <v>21.96</v>
+        <v>22.204</v>
       </c>
       <c r="F92">
-        <v>21.96</v>
+        <v>22.204</v>
       </c>
       <c r="G92">
         <v>0.06900000000000001</v>
@@ -8819,28 +8819,28 @@
         <v>32.9</v>
       </c>
       <c r="M92">
-        <v>1.104588</v>
+        <v>1.1168612</v>
       </c>
       <c r="N92">
-        <v>31.795412</v>
+        <v>31.7831388</v>
       </c>
       <c r="O92">
-        <v>6.3590824</v>
+        <v>6.35662776</v>
       </c>
       <c r="P92">
-        <v>25.4363296</v>
+        <v>25.42651104</v>
       </c>
       <c r="Q92">
-        <v>29.8363296</v>
+        <v>29.82651104</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7176770092498602</v>
+        <v>0.7905092053745064</v>
       </c>
       <c r="T92">
-        <v>8.048913444592316</v>
+        <v>8.921424387095549</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>29.78486096173415</v>
+        <v>29.45755479731949</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1077642284837056</v>
+        <v>0.1075447560424251</v>
       </c>
       <c r="C93">
-        <v>3.238937730457526</v>
+        <v>3.006895481736411</v>
       </c>
       <c r="D93">
-        <v>25.37393773045753</v>
+        <v>25.38589548173641</v>
       </c>
       <c r="E93">
-        <v>22.204</v>
+        <v>22.448</v>
       </c>
       <c r="F93">
-        <v>22.204</v>
+        <v>22.448</v>
       </c>
       <c r="G93">
         <v>0.06900000000000001</v>
@@ -8901,28 +8901,28 @@
         <v>32.9</v>
       </c>
       <c r="M93">
-        <v>1.1168612</v>
+        <v>1.1291344</v>
       </c>
       <c r="N93">
-        <v>31.7831388</v>
+        <v>31.7708656</v>
       </c>
       <c r="O93">
-        <v>6.35662776</v>
+        <v>6.35417312</v>
       </c>
       <c r="P93">
-        <v>25.42651104</v>
+        <v>25.41669248</v>
       </c>
       <c r="Q93">
-        <v>29.82651104</v>
+        <v>29.81669248</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7905092053745064</v>
+        <v>0.8815494505303143</v>
       </c>
       <c r="T93">
-        <v>8.921424387095549</v>
+        <v>10.01206306522459</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>29.45755479731949</v>
+        <v>29.13736398430515</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1075447560424251</v>
+        <v>0.1073252836011447</v>
       </c>
       <c r="C94">
-        <v>3.006895481736411</v>
+        <v>2.774864508776552</v>
       </c>
       <c r="D94">
-        <v>25.38589548173641</v>
+        <v>25.39786450877655</v>
       </c>
       <c r="E94">
-        <v>22.448</v>
+        <v>22.692</v>
       </c>
       <c r="F94">
-        <v>22.448</v>
+        <v>22.692</v>
       </c>
       <c r="G94">
         <v>0.06900000000000001</v>
@@ -8983,28 +8983,28 @@
         <v>32.9</v>
       </c>
       <c r="M94">
-        <v>1.1291344</v>
+        <v>1.1414076</v>
       </c>
       <c r="N94">
-        <v>31.7708656</v>
+        <v>31.7585924</v>
       </c>
       <c r="O94">
-        <v>6.35417312</v>
+        <v>6.35171848</v>
       </c>
       <c r="P94">
-        <v>25.41669248</v>
+        <v>25.40687392</v>
       </c>
       <c r="Q94">
-        <v>29.81669248</v>
+        <v>29.80687392</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8815494505303143</v>
+        <v>0.9986011943020671</v>
       </c>
       <c r="T94">
-        <v>10.01206306522459</v>
+        <v>11.41431279424764</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>29.13736398430515</v>
+        <v>28.82405899522659</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1073252836011447</v>
+        <v>0.1071058111598642</v>
       </c>
       <c r="C95">
-        <v>2.774864508776552</v>
+        <v>2.542844827534477</v>
       </c>
       <c r="D95">
-        <v>25.39786450877655</v>
+        <v>25.40984482753448</v>
       </c>
       <c r="E95">
-        <v>22.692</v>
+        <v>22.936</v>
       </c>
       <c r="F95">
-        <v>22.692</v>
+        <v>22.936</v>
       </c>
       <c r="G95">
         <v>0.06900000000000001</v>
@@ -9065,28 +9065,28 @@
         <v>32.9</v>
       </c>
       <c r="M95">
-        <v>1.1414076</v>
+        <v>1.1536808</v>
       </c>
       <c r="N95">
-        <v>31.7585924</v>
+        <v>31.7463192</v>
       </c>
       <c r="O95">
-        <v>6.35171848</v>
+        <v>6.34926384</v>
       </c>
       <c r="P95">
-        <v>25.40687392</v>
+        <v>25.39705536</v>
       </c>
       <c r="Q95">
-        <v>29.80687392</v>
+        <v>29.79705536</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9986011943020671</v>
+        <v>1.154670185997738</v>
       </c>
       <c r="T95">
-        <v>11.41431279424764</v>
+        <v>13.28397909961172</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>28.82405899522659</v>
+        <v>28.51742006974547</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1071058111598642</v>
+        <v>0.1068863387185837</v>
       </c>
       <c r="C96">
-        <v>2.542844827534477</v>
+        <v>2.310836453996835</v>
       </c>
       <c r="D96">
-        <v>25.40984482753448</v>
+        <v>25.42183645399684</v>
       </c>
       <c r="E96">
-        <v>22.936</v>
+        <v>23.18</v>
       </c>
       <c r="F96">
-        <v>22.936</v>
+        <v>23.18</v>
       </c>
       <c r="G96">
         <v>0.06900000000000001</v>
@@ -9147,28 +9147,28 @@
         <v>32.9</v>
       </c>
       <c r="M96">
-        <v>1.1536808</v>
+        <v>1.165954</v>
       </c>
       <c r="N96">
-        <v>31.7463192</v>
+        <v>31.734046</v>
       </c>
       <c r="O96">
-        <v>6.34926384</v>
+        <v>6.3468092</v>
       </c>
       <c r="P96">
-        <v>25.39705536</v>
+        <v>25.3872368</v>
       </c>
       <c r="Q96">
-        <v>29.79705536</v>
+        <v>29.7872368</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.154670185997738</v>
+        <v>1.373166774371677</v>
       </c>
       <c r="T96">
-        <v>13.28397909961172</v>
+        <v>15.90151192712142</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>28.51742006974547</v>
+        <v>28.21723670059025</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1068863387185837</v>
+        <v>0.1066668662773033</v>
       </c>
       <c r="C97">
-        <v>2.310836453996835</v>
+        <v>2.078839404180457</v>
       </c>
       <c r="D97">
-        <v>25.42183645399684</v>
+        <v>25.43383940418046</v>
       </c>
       <c r="E97">
-        <v>23.18</v>
+        <v>23.424</v>
       </c>
       <c r="F97">
-        <v>23.18</v>
+        <v>23.424</v>
       </c>
       <c r="G97">
         <v>0.06900000000000001</v>
@@ -9229,28 +9229,28 @@
         <v>32.9</v>
       </c>
       <c r="M97">
-        <v>1.165954</v>
+        <v>1.1782272</v>
       </c>
       <c r="N97">
-        <v>31.734046</v>
+        <v>31.7217728</v>
       </c>
       <c r="O97">
-        <v>6.3468092</v>
+        <v>6.34435456</v>
       </c>
       <c r="P97">
-        <v>25.3872368</v>
+        <v>25.37741824</v>
       </c>
       <c r="Q97">
-        <v>29.7872368</v>
+        <v>29.77741824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.373166774371677</v>
+        <v>1.700911656932586</v>
       </c>
       <c r="T97">
-        <v>15.90151192712142</v>
+        <v>19.82781116838598</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>28.21723670059025</v>
+        <v>27.92330715162577</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1066668662773033</v>
+        <v>0.1064473938360228</v>
       </c>
       <c r="C98">
-        <v>2.078839404180457</v>
+        <v>1.846853694132445</v>
       </c>
       <c r="D98">
-        <v>25.43383940418046</v>
+        <v>25.44585369413245</v>
       </c>
       <c r="E98">
-        <v>23.424</v>
+        <v>23.668</v>
       </c>
       <c r="F98">
-        <v>23.424</v>
+        <v>23.668</v>
       </c>
       <c r="G98">
         <v>0.06900000000000001</v>
@@ -9311,28 +9311,28 @@
         <v>32.9</v>
       </c>
       <c r="M98">
-        <v>1.1782272</v>
+        <v>1.1905004</v>
       </c>
       <c r="N98">
-        <v>31.7217728</v>
+        <v>31.7094996</v>
       </c>
       <c r="O98">
-        <v>6.34435456</v>
+        <v>6.341899919999999</v>
       </c>
       <c r="P98">
-        <v>25.37741824</v>
+        <v>25.36759968</v>
       </c>
       <c r="Q98">
-        <v>29.77741824</v>
+        <v>29.76759968</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.700911656932581</v>
+        <v>2.247153127867426</v>
       </c>
       <c r="T98">
-        <v>19.82781116838593</v>
+        <v>26.37164323716016</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>27.92330715162577</v>
+        <v>27.63543800573272</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1064473938360228</v>
+        <v>0.1062279213947424</v>
       </c>
       <c r="C99">
-        <v>1.846853694132445</v>
+        <v>1.614879339930244</v>
       </c>
       <c r="D99">
-        <v>25.44585369413245</v>
+        <v>25.45787933993024</v>
       </c>
       <c r="E99">
-        <v>23.668</v>
+        <v>23.912</v>
       </c>
       <c r="F99">
-        <v>23.668</v>
+        <v>23.912</v>
       </c>
       <c r="G99">
         <v>0.06900000000000001</v>
@@ -9393,28 +9393,28 @@
         <v>32.9</v>
       </c>
       <c r="M99">
-        <v>1.1905004</v>
+        <v>1.2027736</v>
       </c>
       <c r="N99">
-        <v>31.7094996</v>
+        <v>31.6972264</v>
       </c>
       <c r="O99">
-        <v>6.341899919999999</v>
+        <v>6.33944528</v>
       </c>
       <c r="P99">
-        <v>25.36759968</v>
+        <v>25.35778112</v>
       </c>
       <c r="Q99">
-        <v>29.76759968</v>
+        <v>29.75778112</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.247153127867426</v>
+        <v>3.339636069737117</v>
       </c>
       <c r="T99">
-        <v>26.37164323716016</v>
+        <v>39.45930737470863</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>27.63543800573272</v>
+        <v>27.3534437403681</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1062279213947424</v>
+        <v>0.1060084489534619</v>
       </c>
       <c r="C100">
-        <v>1.614879339930244</v>
+        <v>1.382916357681694</v>
       </c>
       <c r="D100">
-        <v>25.45787933993024</v>
+        <v>25.46991635768169</v>
       </c>
       <c r="E100">
-        <v>23.912</v>
+        <v>24.156</v>
       </c>
       <c r="F100">
-        <v>23.912</v>
+        <v>24.156</v>
       </c>
       <c r="G100">
         <v>0.06900000000000001</v>
@@ -9475,28 +9475,28 @@
         <v>32.9</v>
       </c>
       <c r="M100">
-        <v>1.2027736</v>
+        <v>1.2150468</v>
       </c>
       <c r="N100">
-        <v>31.6972264</v>
+        <v>31.6849532</v>
       </c>
       <c r="O100">
-        <v>6.33944528</v>
+        <v>6.33699064</v>
       </c>
       <c r="P100">
-        <v>25.35778112</v>
+        <v>25.34796256</v>
       </c>
       <c r="Q100">
-        <v>29.75778112</v>
+        <v>29.74796256</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.339636069737117</v>
+        <v>6.617084895346187</v>
       </c>
       <c r="T100">
-        <v>39.45930737470863</v>
+        <v>78.72229978735402</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>27.3534437403681</v>
+        <v>27.07714632884923</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1060084489534619</v>
-      </c>
-      <c r="C101">
-        <v>1.382916357681694</v>
-      </c>
-      <c r="D101">
-        <v>25.46991635768169</v>
-      </c>
-      <c r="E101">
-        <v>24.156</v>
-      </c>
-      <c r="F101">
-        <v>24.156</v>
-      </c>
-      <c r="G101">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="H101">
-        <v>24.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37.3</v>
-      </c>
-      <c r="K101">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>32.9</v>
-      </c>
-      <c r="M101">
-        <v>1.2150468</v>
-      </c>
-      <c r="N101">
-        <v>31.6849532</v>
-      </c>
-      <c r="O101">
-        <v>6.33699064</v>
-      </c>
-      <c r="P101">
-        <v>25.34796256</v>
-      </c>
-      <c r="Q101">
-        <v>29.74796256</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.617084895346187</v>
-      </c>
-      <c r="T101">
-        <v>78.72229978735402</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.04024</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>27.07714632884923</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
